--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124454215</v>
+        <v>124449907</v>
       </c>
       <c r="B27" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,38 +3547,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699929</v>
+        <v>699754</v>
       </c>
       <c r="R27" t="n">
-        <v>6660329</v>
+        <v>6660376</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3630,17 +3635,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124450058</v>
+        <v>124474453</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,41 +3654,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699808</v>
+        <v>699934</v>
       </c>
       <c r="R28" t="n">
-        <v>6660347</v>
+        <v>6660275</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3727,19 +3732,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124452710</v>
+        <v>124446528</v>
       </c>
       <c r="B29" t="n">
         <v>100279</v>
@@ -3779,10 +3784,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699855</v>
+        <v>699808</v>
       </c>
       <c r="R29" t="n">
-        <v>6660145</v>
+        <v>6660347</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124474453</v>
+        <v>124447074</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,34 +3862,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699934</v>
+        <v>699804</v>
       </c>
       <c r="R30" t="n">
-        <v>6660275</v>
+        <v>6660392</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,22 +3941,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124474451</v>
+        <v>124450058</v>
       </c>
       <c r="B31" t="n">
-        <v>90445</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3955,44 +3965,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4189</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699943</v>
+        <v>699808</v>
       </c>
       <c r="R31" t="n">
-        <v>6660307</v>
+        <v>6660347</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4030,33 +4037,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124447516</v>
+        <v>124446732</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4065,47 +4067,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699800</v>
+        <v>699804</v>
       </c>
       <c r="R32" t="n">
-        <v>6660415</v>
+        <v>6660392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4164,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124445043</v>
+        <v>124445128</v>
       </c>
       <c r="B33" t="n">
-        <v>5176</v>
+        <v>92326</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4180,29 +4173,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
@@ -4373,10 +4361,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474452</v>
+        <v>124447694</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,38 +4373,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699807</v>
+        <v>699777</v>
       </c>
       <c r="R35" t="n">
-        <v>6660377</v>
+        <v>6660425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4463,22 +4451,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124447694</v>
+        <v>124444867</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>95455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4487,41 +4475,45 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699777</v>
+        <v>699944</v>
       </c>
       <c r="R36" t="n">
-        <v>6660425</v>
+        <v>6660374</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4559,6 +4551,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4577,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124445128</v>
+        <v>124474451</v>
       </c>
       <c r="B37" t="n">
-        <v>92326</v>
+        <v>90445</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4593,34 +4586,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>4189</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699954</v>
+        <v>699943</v>
       </c>
       <c r="R37" t="n">
-        <v>6660370</v>
+        <v>6660307</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4661,28 +4657,33 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124451555</v>
+        <v>124452710</v>
       </c>
       <c r="B38" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4691,50 +4692,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699672</v>
+        <v>699855</v>
       </c>
       <c r="R38" t="n">
-        <v>6660331</v>
+        <v>6660145</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4790,10 +4782,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124444974</v>
+        <v>124451081</v>
       </c>
       <c r="B39" t="n">
-        <v>5196</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4802,20 +4794,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4826,7 +4818,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4835,10 +4827,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R39" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4897,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124446732</v>
+        <v>124445043</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4909,38 +4901,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R40" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4999,10 +4996,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124449907</v>
+        <v>124451555</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>90448</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5015,27 +5012,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2008</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5044,13 +5045,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699754</v>
+        <v>699672</v>
       </c>
       <c r="R41" t="n">
-        <v>6660376</v>
+        <v>6660331</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5106,7 +5107,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124444956</v>
+        <v>124474452</v>
       </c>
       <c r="B42" t="n">
         <v>100279</v>
@@ -5142,17 +5143,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699944</v>
+        <v>699807</v>
       </c>
       <c r="R42" t="n">
-        <v>6660374</v>
+        <v>6660377</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5196,22 +5197,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124447074</v>
+        <v>124447516</v>
       </c>
       <c r="B43" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5220,31 +5221,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5253,10 +5258,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699804</v>
+        <v>699800</v>
       </c>
       <c r="R43" t="n">
-        <v>6660392</v>
+        <v>6660415</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5417,10 +5422,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124451595</v>
+        <v>124444974</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5433,34 +5438,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699683</v>
+        <v>699954</v>
       </c>
       <c r="R45" t="n">
-        <v>6660350</v>
+        <v>6660370</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5519,10 +5529,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124444867</v>
+        <v>124454215</v>
       </c>
       <c r="B46" t="n">
-        <v>95455</v>
+        <v>96979</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5535,38 +5545,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2818</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699944</v>
+        <v>699929</v>
       </c>
       <c r="R46" t="n">
-        <v>6660374</v>
+        <v>6660329</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5607,7 +5613,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5626,10 +5631,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124451081</v>
+        <v>124444956</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5638,46 +5643,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R47" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124446528</v>
+        <v>124451595</v>
       </c>
       <c r="B48" t="n">
         <v>100279</v>
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699808</v>
+        <v>699683</v>
       </c>
       <c r="R48" t="n">
-        <v>6660347</v>
+        <v>6660350</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124449907</v>
+        <v>124444956</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,43 +3547,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699754</v>
+        <v>699944</v>
       </c>
       <c r="R27" t="n">
-        <v>6660376</v>
+        <v>6660374</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3635,17 +3630,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124474453</v>
+        <v>124451081</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,38 +3649,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699934</v>
+        <v>699683</v>
       </c>
       <c r="R28" t="n">
-        <v>6660275</v>
+        <v>6660350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3732,19 +3732,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124446528</v>
+        <v>124451595</v>
       </c>
       <c r="B29" t="n">
         <v>100279</v>
@@ -3784,13 +3784,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699808</v>
+        <v>699683</v>
       </c>
       <c r="R29" t="n">
-        <v>6660347</v>
+        <v>6660350</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124447074</v>
+        <v>124454215</v>
       </c>
       <c r="B30" t="n">
-        <v>5176</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,42 +3862,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699804</v>
+        <v>699929</v>
       </c>
       <c r="R30" t="n">
-        <v>6660392</v>
+        <v>6660329</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3953,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124450058</v>
+        <v>124444867</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>95455</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3965,38 +3960,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699808</v>
+        <v>699944</v>
       </c>
       <c r="R31" t="n">
-        <v>6660347</v>
+        <v>6660374</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4037,6 +4036,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124446732</v>
+        <v>124449907</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,37 +4071,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699804</v>
+        <v>699754</v>
       </c>
       <c r="R32" t="n">
-        <v>6660392</v>
+        <v>6660376</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4157,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124445128</v>
+        <v>124474452</v>
       </c>
       <c r="B33" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4173,34 +4178,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699954</v>
+        <v>699807</v>
       </c>
       <c r="R33" t="n">
-        <v>6660370</v>
+        <v>6660377</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4247,19 +4252,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124450248</v>
+        <v>124446528</v>
       </c>
       <c r="B34" t="n">
         <v>100279</v>
@@ -4299,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699796</v>
+        <v>699808</v>
       </c>
       <c r="R34" t="n">
-        <v>6660315</v>
+        <v>6660347</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4361,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124447694</v>
+        <v>124474453</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4373,38 +4378,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699777</v>
+        <v>699934</v>
       </c>
       <c r="R35" t="n">
-        <v>6660425</v>
+        <v>6660275</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4451,22 +4456,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124444867</v>
+        <v>124450248</v>
       </c>
       <c r="B36" t="n">
-        <v>95455</v>
+        <v>100279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4479,38 +4484,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699944</v>
+        <v>699796</v>
       </c>
       <c r="R36" t="n">
-        <v>6660374</v>
+        <v>6660315</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4551,7 +4552,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124474451</v>
+        <v>124445043</v>
       </c>
       <c r="B37" t="n">
-        <v>90445</v>
+        <v>5176</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,37 +4586,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4189</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699943</v>
+        <v>699954</v>
       </c>
       <c r="R37" t="n">
-        <v>6660307</v>
+        <v>6660370</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4657,33 +4659,28 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124452710</v>
+        <v>124446732</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4692,25 +4689,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699855</v>
+        <v>699804</v>
       </c>
       <c r="R38" t="n">
-        <v>6660145</v>
+        <v>6660392</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,10 +4779,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124451081</v>
+        <v>124450058</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,42 +4795,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699683</v>
+        <v>699808</v>
       </c>
       <c r="R39" t="n">
-        <v>6660350</v>
+        <v>6660347</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4889,10 +4881,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124445043</v>
+        <v>124474451</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>90445</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4905,39 +4897,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>4189</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699954</v>
+        <v>699943</v>
       </c>
       <c r="R40" t="n">
-        <v>6660370</v>
+        <v>6660307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4978,28 +4968,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124451555</v>
+        <v>124444974</v>
       </c>
       <c r="B41" t="n">
-        <v>90448</v>
+        <v>5196</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5008,35 +5003,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2008</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5045,10 +5036,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699672</v>
+        <v>699954</v>
       </c>
       <c r="R41" t="n">
-        <v>6660331</v>
+        <v>6660370</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5107,10 +5098,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124474452</v>
+        <v>124445128</v>
       </c>
       <c r="B42" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5123,34 +5114,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699807</v>
+        <v>699954</v>
       </c>
       <c r="R42" t="n">
-        <v>6660377</v>
+        <v>6660370</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,22 +5188,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124447516</v>
+        <v>124444432</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>92326</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5221,50 +5212,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699800</v>
+        <v>699938</v>
       </c>
       <c r="R43" t="n">
-        <v>6660415</v>
+        <v>6660298</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5320,10 +5302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124444432</v>
+        <v>124447516</v>
       </c>
       <c r="B44" t="n">
-        <v>92326</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5332,41 +5314,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699938</v>
+        <v>699800</v>
       </c>
       <c r="R44" t="n">
-        <v>6660298</v>
+        <v>6660415</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5422,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124444974</v>
+        <v>124452710</v>
       </c>
       <c r="B45" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5438,42 +5429,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699954</v>
+        <v>699855</v>
       </c>
       <c r="R45" t="n">
-        <v>6660370</v>
+        <v>6660145</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5529,10 +5515,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124454215</v>
+        <v>124447694</v>
       </c>
       <c r="B46" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5541,25 +5527,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5569,13 +5555,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699929</v>
+        <v>699777</v>
       </c>
       <c r="R46" t="n">
-        <v>6660329</v>
+        <v>6660425</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5631,10 +5617,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124444956</v>
+        <v>124447074</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5647,37 +5633,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699944</v>
+        <v>699804</v>
       </c>
       <c r="R47" t="n">
-        <v>6660374</v>
+        <v>6660392</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5733,10 +5724,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124451595</v>
+        <v>124451555</v>
       </c>
       <c r="B48" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5745,38 +5736,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699683</v>
+        <v>699672</v>
       </c>
       <c r="R48" t="n">
-        <v>6660350</v>
+        <v>6660331</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,7 +3535,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124444956</v>
+        <v>124446528</v>
       </c>
       <c r="B27" t="n">
         <v>100279</v>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699944</v>
+        <v>699808</v>
       </c>
       <c r="R27" t="n">
-        <v>6660374</v>
+        <v>6660347</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124451081</v>
+        <v>124447074</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>5176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,31 +3649,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699683</v>
+        <v>699804</v>
       </c>
       <c r="R28" t="n">
-        <v>6660350</v>
+        <v>6660392</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124451595</v>
+        <v>124474452</v>
       </c>
       <c r="B29" t="n">
         <v>100279</v>
@@ -3780,14 +3780,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699683</v>
+        <v>699807</v>
       </c>
       <c r="R29" t="n">
-        <v>6660350</v>
+        <v>6660377</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3834,22 +3834,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124454215</v>
+        <v>124444974</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>5196</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,37 +3862,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699929</v>
+        <v>699954</v>
       </c>
       <c r="R30" t="n">
-        <v>6660329</v>
+        <v>6660370</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3948,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124444867</v>
+        <v>124454215</v>
       </c>
       <c r="B31" t="n">
-        <v>95455</v>
+        <v>96979</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,38 +3969,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2818</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699944</v>
+        <v>699929</v>
       </c>
       <c r="R31" t="n">
-        <v>6660374</v>
+        <v>6660329</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4036,7 +4037,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124449907</v>
+        <v>124474451</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>90445</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4067,46 +4067,44 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>4189</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699754</v>
+        <v>699943</v>
       </c>
       <c r="R32" t="n">
-        <v>6660376</v>
+        <v>6660307</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4144,25 +4142,30 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124474452</v>
+        <v>124450248</v>
       </c>
       <c r="B33" t="n">
         <v>100279</v>
@@ -4198,17 +4201,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699807</v>
+        <v>699796</v>
       </c>
       <c r="R33" t="n">
-        <v>6660377</v>
+        <v>6660315</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4252,22 +4255,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124446528</v>
+        <v>124445043</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,37 +4283,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699808</v>
+        <v>699954</v>
       </c>
       <c r="R34" t="n">
-        <v>6660347</v>
+        <v>6660370</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4366,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474453</v>
+        <v>124447694</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4378,38 +4386,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699934</v>
+        <v>699777</v>
       </c>
       <c r="R35" t="n">
-        <v>6660275</v>
+        <v>6660425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,19 +4464,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124450248</v>
+        <v>124474453</v>
       </c>
       <c r="B36" t="n">
         <v>100279</v>
@@ -4504,17 +4512,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699796</v>
+        <v>699934</v>
       </c>
       <c r="R36" t="n">
-        <v>6660315</v>
+        <v>6660275</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,22 +4566,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124445043</v>
+        <v>124444867</v>
       </c>
       <c r="B37" t="n">
-        <v>5176</v>
+        <v>95455</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,42 +4594,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699954</v>
+        <v>699944</v>
       </c>
       <c r="R37" t="n">
-        <v>6660370</v>
+        <v>6660374</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4659,6 +4666,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4677,10 +4685,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124446732</v>
+        <v>124444956</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4689,25 +4697,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4717,13 +4725,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699804</v>
+        <v>699944</v>
       </c>
       <c r="R38" t="n">
-        <v>6660392</v>
+        <v>6660374</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4779,7 +4787,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124450058</v>
+        <v>124446732</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4819,13 +4827,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699808</v>
+        <v>699804</v>
       </c>
       <c r="R39" t="n">
-        <v>6660347</v>
+        <v>6660392</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4881,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124474451</v>
+        <v>124452710</v>
       </c>
       <c r="B40" t="n">
-        <v>90445</v>
+        <v>100279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4897,40 +4905,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699943</v>
+        <v>699855</v>
       </c>
       <c r="R40" t="n">
-        <v>6660307</v>
+        <v>6660145</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4968,33 +4973,28 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124444974</v>
+        <v>124450058</v>
       </c>
       <c r="B41" t="n">
-        <v>5196</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5003,46 +5003,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699954</v>
+        <v>699808</v>
       </c>
       <c r="R41" t="n">
-        <v>6660370</v>
+        <v>6660347</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5098,10 +5093,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124445128</v>
+        <v>124451595</v>
       </c>
       <c r="B42" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5114,21 +5109,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5138,10 +5133,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R42" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5200,10 +5195,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124444432</v>
+        <v>124451081</v>
       </c>
       <c r="B43" t="n">
-        <v>92326</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5212,41 +5207,46 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699938</v>
+        <v>699683</v>
       </c>
       <c r="R43" t="n">
-        <v>6660298</v>
+        <v>6660350</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124452710</v>
+        <v>124449907</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5425,38 +5425,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699855</v>
+        <v>699754</v>
       </c>
       <c r="R45" t="n">
-        <v>6660145</v>
+        <v>6660376</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5515,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124447694</v>
+        <v>124444432</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>92326</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5527,25 +5532,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5555,13 +5560,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699777</v>
+        <v>699938</v>
       </c>
       <c r="R46" t="n">
-        <v>6660425</v>
+        <v>6660298</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5617,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124447074</v>
+        <v>124445128</v>
       </c>
       <c r="B47" t="n">
-        <v>5176</v>
+        <v>92326</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5633,39 +5638,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R47" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124446528</v>
+        <v>124449907</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,38 +3547,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699808</v>
+        <v>699754</v>
       </c>
       <c r="R27" t="n">
-        <v>6660347</v>
+        <v>6660376</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3637,10 +3642,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124447074</v>
+        <v>124444974</v>
       </c>
       <c r="B28" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3653,27 +3658,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3682,10 +3687,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R28" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,7 +3749,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124474452</v>
+        <v>124452710</v>
       </c>
       <c r="B29" t="n">
         <v>100279</v>
@@ -3780,17 +3785,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699807</v>
+        <v>699855</v>
       </c>
       <c r="R29" t="n">
-        <v>6660377</v>
+        <v>6660145</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3834,22 +3839,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124444974</v>
+        <v>124474453</v>
       </c>
       <c r="B30" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,39 +3867,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699954</v>
+        <v>699934</v>
       </c>
       <c r="R30" t="n">
-        <v>6660370</v>
+        <v>6660275</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3941,22 +3941,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124454215</v>
+        <v>124450248</v>
       </c>
       <c r="B31" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,21 +3969,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699929</v>
+        <v>699796</v>
       </c>
       <c r="R31" t="n">
-        <v>6660329</v>
+        <v>6660315</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124474451</v>
+        <v>124444432</v>
       </c>
       <c r="B32" t="n">
-        <v>90445</v>
+        <v>92326</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,40 +4071,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4189</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699943</v>
+        <v>699938</v>
       </c>
       <c r="R32" t="n">
-        <v>6660307</v>
+        <v>6660298</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4142,30 +4139,25 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124450248</v>
+        <v>124446528</v>
       </c>
       <c r="B33" t="n">
         <v>100279</v>
@@ -4205,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699796</v>
+        <v>699808</v>
       </c>
       <c r="R33" t="n">
-        <v>6660315</v>
+        <v>6660347</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4267,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124445043</v>
+        <v>124451081</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4279,31 +4271,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4312,10 +4304,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R34" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4374,7 +4366,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124447694</v>
+        <v>124446732</v>
       </c>
       <c r="B35" t="n">
         <v>91012</v>
@@ -4414,10 +4406,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699777</v>
+        <v>699804</v>
       </c>
       <c r="R35" t="n">
-        <v>6660425</v>
+        <v>6660392</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4476,7 +4468,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124474453</v>
+        <v>124474452</v>
       </c>
       <c r="B36" t="n">
         <v>100279</v>
@@ -4516,10 +4508,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699934</v>
+        <v>699807</v>
       </c>
       <c r="R36" t="n">
-        <v>6660275</v>
+        <v>6660377</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124444867</v>
+        <v>124445128</v>
       </c>
       <c r="B37" t="n">
-        <v>95455</v>
+        <v>92326</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,41 +4586,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699944</v>
+        <v>699954</v>
       </c>
       <c r="R37" t="n">
-        <v>6660374</v>
+        <v>6660370</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4666,7 +4654,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4685,10 +4672,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124444956</v>
+        <v>124474451</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>90445</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4701,37 +4688,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699944</v>
+        <v>699943</v>
       </c>
       <c r="R38" t="n">
-        <v>6660374</v>
+        <v>6660307</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4769,25 +4759,30 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124446732</v>
+        <v>124450058</v>
       </c>
       <c r="B39" t="n">
         <v>91012</v>
@@ -4827,13 +4822,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699804</v>
+        <v>699808</v>
       </c>
       <c r="R39" t="n">
-        <v>6660392</v>
+        <v>6660347</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4889,10 +4884,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124452710</v>
+        <v>124447694</v>
       </c>
       <c r="B40" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4901,25 +4896,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4929,13 +4924,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699855</v>
+        <v>699777</v>
       </c>
       <c r="R40" t="n">
-        <v>6660145</v>
+        <v>6660425</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4991,10 +4986,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124450058</v>
+        <v>124451595</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5003,25 +4998,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5031,13 +5026,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699808</v>
+        <v>699683</v>
       </c>
       <c r="R41" t="n">
-        <v>6660347</v>
+        <v>6660350</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5093,10 +5088,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124451595</v>
+        <v>124444867</v>
       </c>
       <c r="B42" t="n">
-        <v>100279</v>
+        <v>95455</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5109,37 +5104,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R42" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5177,6 +5176,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5195,10 +5195,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124451081</v>
+        <v>124454215</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5207,46 +5207,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699683</v>
+        <v>699929</v>
       </c>
       <c r="R43" t="n">
-        <v>6660350</v>
+        <v>6660329</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,10 +5297,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124447516</v>
+        <v>124445043</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5314,35 +5309,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5351,10 +5342,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699800</v>
+        <v>699954</v>
       </c>
       <c r="R44" t="n">
-        <v>6660415</v>
+        <v>6660370</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,10 +5404,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124449907</v>
+        <v>124447074</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>5176</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5425,31 +5416,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5458,13 +5449,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699754</v>
+        <v>699804</v>
       </c>
       <c r="R45" t="n">
-        <v>6660376</v>
+        <v>6660392</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5520,10 +5511,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124444432</v>
+        <v>124444956</v>
       </c>
       <c r="B46" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5536,21 +5527,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,10 +5551,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699938</v>
+        <v>699944</v>
       </c>
       <c r="R46" t="n">
-        <v>6660298</v>
+        <v>6660374</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5622,10 +5613,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124445128</v>
+        <v>124451555</v>
       </c>
       <c r="B47" t="n">
-        <v>92326</v>
+        <v>90448</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,38 +5625,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>2008</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699954</v>
+        <v>699672</v>
       </c>
       <c r="R47" t="n">
-        <v>6660370</v>
+        <v>6660331</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5721,117 +5721,6 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>124451555</v>
-      </c>
-      <c r="B48" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Fyrflikig jordstjärna</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Geastrum quadrifidum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Svedjan, Upl</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>699672</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6660331</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Edebo</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124449907</v>
+        <v>124444974</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>5196</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,20 +3547,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3571,7 +3571,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3580,13 +3580,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699754</v>
+        <v>699954</v>
       </c>
       <c r="R27" t="n">
-        <v>6660376</v>
+        <v>6660370</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124444974</v>
+        <v>124449907</v>
       </c>
       <c r="B28" t="n">
-        <v>5196</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,20 +3654,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3678,7 +3678,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3687,13 +3687,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699954</v>
+        <v>699754</v>
       </c>
       <c r="R28" t="n">
-        <v>6660370</v>
+        <v>6660376</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4157,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124446528</v>
+        <v>124451081</v>
       </c>
       <c r="B33" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,41 +4169,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699808</v>
+        <v>699683</v>
       </c>
       <c r="R33" t="n">
-        <v>6660347</v>
+        <v>6660350</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4259,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124451081</v>
+        <v>124446528</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4271,46 +4276,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699683</v>
+        <v>699808</v>
       </c>
       <c r="R34" t="n">
-        <v>6660350</v>
+        <v>6660347</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124446732</v>
+        <v>124474452</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4378,38 +4378,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699804</v>
+        <v>699807</v>
       </c>
       <c r="R35" t="n">
-        <v>6660392</v>
+        <v>6660377</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,22 +4456,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124474452</v>
+        <v>124446732</v>
       </c>
       <c r="B36" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,38 +4480,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699807</v>
+        <v>699804</v>
       </c>
       <c r="R36" t="n">
-        <v>6660377</v>
+        <v>6660392</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4558,12 +4558,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5511,10 +5511,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124444956</v>
+        <v>124451555</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5523,41 +5523,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699944</v>
+        <v>699672</v>
       </c>
       <c r="R46" t="n">
-        <v>6660374</v>
+        <v>6660331</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5613,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124451555</v>
+        <v>124444956</v>
       </c>
       <c r="B47" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5625,50 +5634,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699672</v>
+        <v>699944</v>
       </c>
       <c r="R47" t="n">
-        <v>6660331</v>
+        <v>6660374</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124444974</v>
+        <v>124451555</v>
       </c>
       <c r="B27" t="n">
-        <v>5196</v>
+        <v>90448</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,31 +3547,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>2008</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3580,10 +3584,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699954</v>
+        <v>699672</v>
       </c>
       <c r="R27" t="n">
-        <v>6660370</v>
+        <v>6660331</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,10 +3646,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124449907</v>
+        <v>124452710</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,43 +3658,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699754</v>
+        <v>699855</v>
       </c>
       <c r="R28" t="n">
-        <v>6660376</v>
+        <v>6660145</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3749,7 +3748,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124452710</v>
+        <v>124446528</v>
       </c>
       <c r="B29" t="n">
         <v>100279</v>
@@ -3789,10 +3788,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699855</v>
+        <v>699808</v>
       </c>
       <c r="R29" t="n">
-        <v>6660145</v>
+        <v>6660347</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3851,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124474453</v>
+        <v>124445128</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,34 +3866,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699934</v>
+        <v>699954</v>
       </c>
       <c r="R30" t="n">
-        <v>6660275</v>
+        <v>6660370</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3941,19 +3940,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124450248</v>
+        <v>124474452</v>
       </c>
       <c r="B31" t="n">
         <v>100279</v>
@@ -3989,17 +3988,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699796</v>
+        <v>699807</v>
       </c>
       <c r="R31" t="n">
-        <v>6660315</v>
+        <v>6660377</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4043,22 +4042,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124444432</v>
+        <v>124449907</v>
       </c>
       <c r="B32" t="n">
-        <v>92326</v>
+        <v>57529</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4067,38 +4066,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699938</v>
+        <v>699754</v>
       </c>
       <c r="R32" t="n">
-        <v>6660298</v>
+        <v>6660376</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4157,10 +4161,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124451081</v>
+        <v>124444867</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>95455</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4169,46 +4173,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R33" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4246,6 +4249,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4264,7 +4268,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124446528</v>
+        <v>124450248</v>
       </c>
       <c r="B34" t="n">
         <v>100279</v>
@@ -4304,10 +4308,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699808</v>
+        <v>699796</v>
       </c>
       <c r="R34" t="n">
-        <v>6660347</v>
+        <v>6660315</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4366,10 +4370,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474452</v>
+        <v>124445043</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,34 +4386,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699807</v>
+        <v>699954</v>
       </c>
       <c r="R35" t="n">
-        <v>6660377</v>
+        <v>6660370</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4456,22 +4465,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124446732</v>
+        <v>124474451</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>90445</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4480,38 +4489,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>4189</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699804</v>
+        <v>699943</v>
       </c>
       <c r="R36" t="n">
-        <v>6660392</v>
+        <v>6660307</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4552,28 +4564,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124445128</v>
+        <v>124451595</v>
       </c>
       <c r="B37" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4586,21 +4603,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4610,10 +4627,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R37" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4672,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124474451</v>
+        <v>124451081</v>
       </c>
       <c r="B38" t="n">
-        <v>90445</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4684,41 +4701,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4189</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699943</v>
+        <v>699683</v>
       </c>
       <c r="R38" t="n">
-        <v>6660307</v>
+        <v>6660350</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4759,33 +4778,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124450058</v>
+        <v>124454215</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4794,25 +4808,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4822,10 +4836,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699808</v>
+        <v>699929</v>
       </c>
       <c r="R39" t="n">
-        <v>6660347</v>
+        <v>6660329</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4884,10 +4898,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124447694</v>
+        <v>124444974</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>5196</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4896,38 +4910,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>105930</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699777</v>
+        <v>699954</v>
       </c>
       <c r="R40" t="n">
-        <v>6660425</v>
+        <v>6660370</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4986,7 +5005,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124451595</v>
+        <v>124444956</v>
       </c>
       <c r="B41" t="n">
         <v>100279</v>
@@ -5026,13 +5045,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R41" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5088,10 +5107,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124444867</v>
+        <v>124474453</v>
       </c>
       <c r="B42" t="n">
-        <v>95455</v>
+        <v>100279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5104,41 +5123,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699944</v>
+        <v>699934</v>
       </c>
       <c r="R42" t="n">
-        <v>6660374</v>
+        <v>6660275</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5176,29 +5191,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124454215</v>
+        <v>124444432</v>
       </c>
       <c r="B43" t="n">
-        <v>96979</v>
+        <v>92326</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5211,21 +5225,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5235,10 +5249,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699929</v>
+        <v>699938</v>
       </c>
       <c r="R43" t="n">
-        <v>6660329</v>
+        <v>6660298</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5297,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124445043</v>
+        <v>124447694</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5309,43 +5323,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699954</v>
+        <v>699777</v>
       </c>
       <c r="R44" t="n">
-        <v>6660370</v>
+        <v>6660425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5511,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124451555</v>
+        <v>124450058</v>
       </c>
       <c r="B46" t="n">
-        <v>90448</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5527,46 +5536,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2008</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699672</v>
+        <v>699808</v>
       </c>
       <c r="R46" t="n">
-        <v>6660331</v>
+        <v>6660347</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5622,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124444956</v>
+        <v>124446732</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,25 +5634,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699944</v>
+        <v>699804</v>
       </c>
       <c r="R47" t="n">
-        <v>6660374</v>
+        <v>6660392</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -4268,10 +4268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124450248</v>
+        <v>124474451</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>90445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,37 +4284,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699796</v>
+        <v>699943</v>
       </c>
       <c r="R34" t="n">
-        <v>6660315</v>
+        <v>6660307</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4352,21 +4355,26 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4477,10 +4485,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124474451</v>
+        <v>124450248</v>
       </c>
       <c r="B36" t="n">
-        <v>90445</v>
+        <v>100279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4493,40 +4501,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699943</v>
+        <v>699796</v>
       </c>
       <c r="R36" t="n">
-        <v>6660307</v>
+        <v>6660315</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4564,33 +4569,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124451595</v>
+        <v>124451081</v>
       </c>
       <c r="B37" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4599,28 +4599,33 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
@@ -4689,10 +4694,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124451081</v>
+        <v>124451595</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4701,33 +4706,28 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3850,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124445128</v>
+        <v>124474452</v>
       </c>
       <c r="B30" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3866,34 +3866,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699954</v>
+        <v>699807</v>
       </c>
       <c r="R30" t="n">
-        <v>6660370</v>
+        <v>6660377</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3940,22 +3940,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124474452</v>
+        <v>124445128</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3968,34 +3968,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699807</v>
+        <v>699954</v>
       </c>
       <c r="R31" t="n">
-        <v>6660377</v>
+        <v>6660370</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4042,12 +4042,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124451081</v>
+        <v>124451595</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4599,33 +4599,28 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
@@ -4694,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124451595</v>
+        <v>124451081</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4706,28 +4701,33 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124450058</v>
+        <v>124446732</v>
       </c>
       <c r="B46" t="n">
         <v>91012</v>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699808</v>
+        <v>699804</v>
       </c>
       <c r="R46" t="n">
-        <v>6660347</v>
+        <v>6660392</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124446732</v>
+        <v>124450058</v>
       </c>
       <c r="B47" t="n">
         <v>91012</v>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699804</v>
+        <v>699808</v>
       </c>
       <c r="R47" t="n">
-        <v>6660392</v>
+        <v>6660347</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124451555</v>
+        <v>124452710</v>
       </c>
       <c r="B27" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,50 +3547,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699672</v>
+        <v>699855</v>
       </c>
       <c r="R27" t="n">
-        <v>6660331</v>
+        <v>6660145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3646,7 +3637,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124452710</v>
+        <v>124444956</v>
       </c>
       <c r="B28" t="n">
         <v>100279</v>
@@ -3686,10 +3677,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699855</v>
+        <v>699944</v>
       </c>
       <c r="R28" t="n">
-        <v>6660145</v>
+        <v>6660374</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3748,10 +3739,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124446528</v>
+        <v>124449907</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,38 +3751,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699808</v>
+        <v>699754</v>
       </c>
       <c r="R29" t="n">
-        <v>6660347</v>
+        <v>6660376</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3850,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124474452</v>
+        <v>124454215</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3866,37 +3862,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699807</v>
+        <v>699929</v>
       </c>
       <c r="R30" t="n">
-        <v>6660377</v>
+        <v>6660329</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3940,22 +3936,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124445128</v>
+        <v>124447694</v>
       </c>
       <c r="B31" t="n">
-        <v>92326</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,25 +3960,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3992,10 +3988,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699954</v>
+        <v>699777</v>
       </c>
       <c r="R31" t="n">
-        <v>6660370</v>
+        <v>6660425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4054,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124449907</v>
+        <v>124445128</v>
       </c>
       <c r="B32" t="n">
-        <v>57529</v>
+        <v>92326</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,46 +4062,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699754</v>
+        <v>699954</v>
       </c>
       <c r="R32" t="n">
-        <v>6660376</v>
+        <v>6660370</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4268,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124474451</v>
+        <v>124445043</v>
       </c>
       <c r="B34" t="n">
-        <v>90445</v>
+        <v>5176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,37 +4275,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699943</v>
+        <v>699954</v>
       </c>
       <c r="R34" t="n">
-        <v>6660307</v>
+        <v>6660370</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4355,33 +4348,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124445043</v>
+        <v>124474451</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>90445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4394,39 +4382,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>4189</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699954</v>
+        <v>699943</v>
       </c>
       <c r="R35" t="n">
-        <v>6660370</v>
+        <v>6660307</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4467,28 +4453,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124450248</v>
+        <v>124444432</v>
       </c>
       <c r="B36" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4501,21 +4492,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4525,10 +4516,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699796</v>
+        <v>699938</v>
       </c>
       <c r="R36" t="n">
-        <v>6660315</v>
+        <v>6660298</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4587,7 +4578,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124451595</v>
+        <v>124474453</v>
       </c>
       <c r="B37" t="n">
         <v>100279</v>
@@ -4623,14 +4614,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699683</v>
+        <v>699934</v>
       </c>
       <c r="R37" t="n">
-        <v>6660350</v>
+        <v>6660275</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4677,22 +4668,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124451081</v>
+        <v>124450248</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4701,46 +4692,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699683</v>
+        <v>699796</v>
       </c>
       <c r="R38" t="n">
-        <v>6660350</v>
+        <v>6660315</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4796,10 +4782,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124454215</v>
+        <v>124446732</v>
       </c>
       <c r="B39" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4808,25 +4794,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4836,13 +4822,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699929</v>
+        <v>699804</v>
       </c>
       <c r="R39" t="n">
-        <v>6660329</v>
+        <v>6660392</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,10 +4884,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124444974</v>
+        <v>124451081</v>
       </c>
       <c r="B40" t="n">
-        <v>5196</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,20 +4896,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4934,7 +4920,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4943,10 +4929,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R40" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5005,10 +4991,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124444956</v>
+        <v>124444974</v>
       </c>
       <c r="B41" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5021,37 +5007,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699944</v>
+        <v>699954</v>
       </c>
       <c r="R41" t="n">
-        <v>6660374</v>
+        <v>6660370</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5107,7 +5098,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124474453</v>
+        <v>124451595</v>
       </c>
       <c r="B42" t="n">
         <v>100279</v>
@@ -5143,14 +5134,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699934</v>
+        <v>699683</v>
       </c>
       <c r="R42" t="n">
-        <v>6660275</v>
+        <v>6660350</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,22 +5188,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124444432</v>
+        <v>124450058</v>
       </c>
       <c r="B43" t="n">
-        <v>92326</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5221,25 +5212,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5249,10 +5240,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699938</v>
+        <v>699808</v>
       </c>
       <c r="R43" t="n">
-        <v>6660298</v>
+        <v>6660347</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5311,10 +5302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124447694</v>
+        <v>124451555</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>90448</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5327,34 +5318,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>2008</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699777</v>
+        <v>699672</v>
       </c>
       <c r="R44" t="n">
-        <v>6660425</v>
+        <v>6660331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124447074</v>
+        <v>124474452</v>
       </c>
       <c r="B45" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5429,39 +5429,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699804</v>
+        <v>699807</v>
       </c>
       <c r="R45" t="n">
-        <v>6660392</v>
+        <v>6660377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5508,22 +5503,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124446732</v>
+        <v>124446528</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5532,25 +5527,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5560,13 +5555,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699804</v>
+        <v>699808</v>
       </c>
       <c r="R46" t="n">
-        <v>6660392</v>
+        <v>6660347</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5622,10 +5617,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124450058</v>
+        <v>124447074</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,41 +5629,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699808</v>
+        <v>699804</v>
       </c>
       <c r="R47" t="n">
-        <v>6660347</v>
+        <v>6660392</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124452710</v>
+        <v>124446732</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,25 +3547,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699855</v>
+        <v>699804</v>
       </c>
       <c r="R27" t="n">
-        <v>6660145</v>
+        <v>6660392</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124444956</v>
+        <v>124444974</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3653,37 +3653,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699944</v>
+        <v>699954</v>
       </c>
       <c r="R28" t="n">
-        <v>6660374</v>
+        <v>6660370</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3739,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124449907</v>
+        <v>124444432</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>92326</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,43 +3756,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699754</v>
+        <v>699938</v>
       </c>
       <c r="R29" t="n">
-        <v>6660376</v>
+        <v>6660298</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124454215</v>
+        <v>124450248</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699929</v>
+        <v>699796</v>
       </c>
       <c r="R30" t="n">
-        <v>6660329</v>
+        <v>6660315</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3948,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124447694</v>
+        <v>124452710</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3960,25 +3960,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699777</v>
+        <v>699855</v>
       </c>
       <c r="R31" t="n">
-        <v>6660425</v>
+        <v>6660145</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124445128</v>
+        <v>124444956</v>
       </c>
       <c r="B32" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,21 +4066,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4090,13 +4090,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699954</v>
+        <v>699944</v>
       </c>
       <c r="R32" t="n">
-        <v>6660370</v>
+        <v>6660374</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4152,10 +4152,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124444867</v>
+        <v>124451081</v>
       </c>
       <c r="B33" t="n">
-        <v>95455</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,45 +4164,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699944</v>
+        <v>699683</v>
       </c>
       <c r="R33" t="n">
-        <v>6660374</v>
+        <v>6660350</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,7 +4241,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4259,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124445043</v>
+        <v>124474451</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>90445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,39 +4275,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699954</v>
+        <v>699943</v>
       </c>
       <c r="R34" t="n">
-        <v>6660370</v>
+        <v>6660307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4348,28 +4346,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474451</v>
+        <v>124445043</v>
       </c>
       <c r="B35" t="n">
-        <v>90445</v>
+        <v>5176</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,37 +4385,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4189</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699943</v>
+        <v>699954</v>
       </c>
       <c r="R35" t="n">
-        <v>6660307</v>
+        <v>6660370</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4453,33 +4458,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124444432</v>
+        <v>124474452</v>
       </c>
       <c r="B36" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,37 +4492,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699938</v>
+        <v>699807</v>
       </c>
       <c r="R36" t="n">
-        <v>6660298</v>
+        <v>6660377</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4566,19 +4566,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124474453</v>
+        <v>124446528</v>
       </c>
       <c r="B37" t="n">
         <v>100279</v>
@@ -4614,17 +4614,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699934</v>
+        <v>699808</v>
       </c>
       <c r="R37" t="n">
-        <v>6660275</v>
+        <v>6660347</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4668,22 +4668,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124450248</v>
+        <v>124454215</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,21 +4696,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699796</v>
+        <v>699929</v>
       </c>
       <c r="R38" t="n">
-        <v>6660315</v>
+        <v>6660329</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124446732</v>
+        <v>124451555</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>90448</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,34 +4798,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>2008</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699804</v>
+        <v>699672</v>
       </c>
       <c r="R39" t="n">
-        <v>6660392</v>
+        <v>6660331</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4884,10 +4893,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124451081</v>
+        <v>124444867</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>95455</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4896,46 +4905,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R40" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4973,6 +4981,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4991,10 +5000,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124444974</v>
+        <v>124447074</v>
       </c>
       <c r="B41" t="n">
-        <v>5196</v>
+        <v>5176</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5007,27 +5016,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5036,10 +5045,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699954</v>
+        <v>699804</v>
       </c>
       <c r="R41" t="n">
-        <v>6660370</v>
+        <v>6660392</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5098,7 +5107,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124451595</v>
+        <v>124474453</v>
       </c>
       <c r="B42" t="n">
         <v>100279</v>
@@ -5134,14 +5143,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699683</v>
+        <v>699934</v>
       </c>
       <c r="R42" t="n">
-        <v>6660350</v>
+        <v>6660275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5188,22 +5197,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124450058</v>
+        <v>124449907</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5216,34 +5225,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699808</v>
+        <v>699754</v>
       </c>
       <c r="R43" t="n">
-        <v>6660347</v>
+        <v>6660376</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5302,10 +5316,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124451555</v>
+        <v>124451595</v>
       </c>
       <c r="B44" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5314,47 +5328,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699672</v>
+        <v>699683</v>
       </c>
       <c r="R44" t="n">
-        <v>6660331</v>
+        <v>6660350</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5413,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124474452</v>
+        <v>124447694</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5425,38 +5430,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699807</v>
+        <v>699777</v>
       </c>
       <c r="R45" t="n">
-        <v>6660377</v>
+        <v>6660425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5503,22 +5508,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124446528</v>
+        <v>124445128</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5531,21 +5536,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5555,13 +5560,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699808</v>
+        <v>699954</v>
       </c>
       <c r="R46" t="n">
-        <v>6660347</v>
+        <v>6660370</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5617,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124447074</v>
+        <v>124450058</v>
       </c>
       <c r="B47" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5629,46 +5634,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699804</v>
+        <v>699808</v>
       </c>
       <c r="R47" t="n">
-        <v>6660392</v>
+        <v>6660347</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124444432</v>
+        <v>124450248</v>
       </c>
       <c r="B29" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,21 +3760,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699938</v>
+        <v>699796</v>
       </c>
       <c r="R29" t="n">
-        <v>6660298</v>
+        <v>6660315</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124450248</v>
+        <v>124444432</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699796</v>
+        <v>699938</v>
       </c>
       <c r="R30" t="n">
-        <v>6660315</v>
+        <v>6660298</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -4369,10 +4369,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124445043</v>
+        <v>124474452</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,39 +4385,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699954</v>
+        <v>699807</v>
       </c>
       <c r="R35" t="n">
-        <v>6660370</v>
+        <v>6660377</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4464,22 +4459,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124474452</v>
+        <v>124445043</v>
       </c>
       <c r="B36" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,34 +4487,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699807</v>
+        <v>699954</v>
       </c>
       <c r="R36" t="n">
-        <v>6660377</v>
+        <v>6660370</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4566,12 +4566,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124446732</v>
+        <v>124449907</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3551,37 +3551,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699804</v>
+        <v>699754</v>
       </c>
       <c r="R27" t="n">
-        <v>6660392</v>
+        <v>6660376</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3637,10 +3642,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124444974</v>
+        <v>124450058</v>
       </c>
       <c r="B28" t="n">
-        <v>5196</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,46 +3654,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699954</v>
+        <v>699808</v>
       </c>
       <c r="R28" t="n">
-        <v>6660370</v>
+        <v>6660347</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124450248</v>
+        <v>124451555</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3756,41 +3756,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699796</v>
+        <v>699672</v>
       </c>
       <c r="R29" t="n">
-        <v>6660315</v>
+        <v>6660331</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3846,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124444432</v>
+        <v>124474453</v>
       </c>
       <c r="B30" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,37 +3871,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699938</v>
+        <v>699934</v>
       </c>
       <c r="R30" t="n">
-        <v>6660298</v>
+        <v>6660275</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3936,22 +3945,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124452710</v>
+        <v>124444432</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,21 +3973,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3988,10 +3997,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699855</v>
+        <v>699938</v>
       </c>
       <c r="R31" t="n">
-        <v>6660145</v>
+        <v>6660298</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4050,10 +4059,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124444956</v>
+        <v>124474451</v>
       </c>
       <c r="B32" t="n">
-        <v>100279</v>
+        <v>90445</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,37 +4075,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699944</v>
+        <v>699943</v>
       </c>
       <c r="R32" t="n">
-        <v>6660374</v>
+        <v>6660307</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4134,28 +4146,33 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124451081</v>
+        <v>124450248</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,46 +4181,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699683</v>
+        <v>699796</v>
       </c>
       <c r="R33" t="n">
-        <v>6660350</v>
+        <v>6660315</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4259,10 +4271,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124474451</v>
+        <v>124474452</v>
       </c>
       <c r="B34" t="n">
-        <v>90445</v>
+        <v>100279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,37 +4287,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699943</v>
+        <v>699807</v>
       </c>
       <c r="R34" t="n">
-        <v>6660307</v>
+        <v>6660377</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4346,7 +4355,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4361,18 +4369,14 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474452</v>
+        <v>124451081</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4381,38 +4385,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699807</v>
+        <v>699683</v>
       </c>
       <c r="R35" t="n">
-        <v>6660377</v>
+        <v>6660350</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4459,22 +4468,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124445043</v>
+        <v>124447694</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4483,43 +4492,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699954</v>
+        <v>699777</v>
       </c>
       <c r="R36" t="n">
-        <v>6660370</v>
+        <v>6660425</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4578,10 +4582,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124446528</v>
+        <v>124444974</v>
       </c>
       <c r="B37" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4594,37 +4598,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699808</v>
+        <v>699954</v>
       </c>
       <c r="R37" t="n">
-        <v>6660347</v>
+        <v>6660370</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4680,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124454215</v>
+        <v>124451595</v>
       </c>
       <c r="B38" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,21 +4705,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4729,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699929</v>
+        <v>699683</v>
       </c>
       <c r="R38" t="n">
-        <v>6660329</v>
+        <v>6660350</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124451555</v>
+        <v>124444956</v>
       </c>
       <c r="B39" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4794,50 +4803,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699672</v>
+        <v>699944</v>
       </c>
       <c r="R39" t="n">
-        <v>6660331</v>
+        <v>6660374</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4893,10 +4893,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124444867</v>
+        <v>124446732</v>
       </c>
       <c r="B40" t="n">
-        <v>95455</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4905,45 +4905,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699944</v>
+        <v>699804</v>
       </c>
       <c r="R40" t="n">
-        <v>6660374</v>
+        <v>6660392</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4981,7 +4977,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5000,7 +4995,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124447074</v>
+        <v>124445043</v>
       </c>
       <c r="B41" t="n">
         <v>5176</v>
@@ -5036,7 +5031,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5045,10 +5040,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R41" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5107,10 +5102,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124474453</v>
+        <v>124454215</v>
       </c>
       <c r="B42" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5123,37 +5118,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699934</v>
+        <v>699929</v>
       </c>
       <c r="R42" t="n">
-        <v>6660275</v>
+        <v>6660329</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5197,22 +5192,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124449907</v>
+        <v>124452710</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5221,43 +5216,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699754</v>
+        <v>699855</v>
       </c>
       <c r="R43" t="n">
-        <v>6660376</v>
+        <v>6660145</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5316,10 +5306,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124451595</v>
+        <v>124445128</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5332,21 +5322,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5356,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699683</v>
+        <v>699954</v>
       </c>
       <c r="R44" t="n">
-        <v>6660350</v>
+        <v>6660370</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5418,10 +5408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124447694</v>
+        <v>124444867</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>95455</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5430,41 +5420,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699777</v>
+        <v>699944</v>
       </c>
       <c r="R45" t="n">
-        <v>6660425</v>
+        <v>6660374</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5502,6 +5496,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5520,10 +5515,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124445128</v>
+        <v>124447074</v>
       </c>
       <c r="B46" t="n">
-        <v>92326</v>
+        <v>5176</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5536,34 +5531,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699954</v>
+        <v>699804</v>
       </c>
       <c r="R46" t="n">
-        <v>6660370</v>
+        <v>6660392</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5622,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124450058</v>
+        <v>124446528</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,25 +5634,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5721,6 +5721,117 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>124447516</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Svedjan, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>699800</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6660415</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3744,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124451555</v>
+        <v>124474453</v>
       </c>
       <c r="B29" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3756,47 +3756,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699672</v>
+        <v>699934</v>
       </c>
       <c r="R29" t="n">
-        <v>6660331</v>
+        <v>6660275</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3843,22 +3834,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124474453</v>
+        <v>124451555</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,38 +3858,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699934</v>
+        <v>699672</v>
       </c>
       <c r="R30" t="n">
-        <v>6660275</v>
+        <v>6660331</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3945,12 +3945,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124449907</v>
+        <v>124450248</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,43 +3547,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699754</v>
+        <v>699796</v>
       </c>
       <c r="R27" t="n">
-        <v>6660376</v>
+        <v>6660315</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3642,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124450058</v>
+        <v>124445128</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>92326</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,25 +3649,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,13 +3677,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699808</v>
+        <v>699954</v>
       </c>
       <c r="R28" t="n">
-        <v>6660347</v>
+        <v>6660370</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3744,7 +3739,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124474453</v>
+        <v>124446528</v>
       </c>
       <c r="B29" t="n">
         <v>100279</v>
@@ -3780,17 +3775,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699934</v>
+        <v>699808</v>
       </c>
       <c r="R29" t="n">
-        <v>6660275</v>
+        <v>6660347</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3834,22 +3829,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124451555</v>
+        <v>124474453</v>
       </c>
       <c r="B30" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,47 +3853,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699672</v>
+        <v>699934</v>
       </c>
       <c r="R30" t="n">
-        <v>6660331</v>
+        <v>6660275</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3945,22 +3931,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124444432</v>
+        <v>124447074</v>
       </c>
       <c r="B31" t="n">
-        <v>92326</v>
+        <v>5176</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,37 +3959,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699938</v>
+        <v>699804</v>
       </c>
       <c r="R31" t="n">
-        <v>6660298</v>
+        <v>6660392</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4059,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124474451</v>
+        <v>124444974</v>
       </c>
       <c r="B32" t="n">
-        <v>90445</v>
+        <v>5196</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4075,37 +4066,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4189</v>
+        <v>105930</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699943</v>
+        <v>699954</v>
       </c>
       <c r="R32" t="n">
-        <v>6660307</v>
+        <v>6660370</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4146,33 +4139,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124450248</v>
+        <v>124444432</v>
       </c>
       <c r="B33" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4185,21 +4173,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4209,10 +4197,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699796</v>
+        <v>699938</v>
       </c>
       <c r="R33" t="n">
-        <v>6660315</v>
+        <v>6660298</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4271,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124474452</v>
+        <v>124451555</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4283,38 +4271,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699807</v>
+        <v>699672</v>
       </c>
       <c r="R34" t="n">
-        <v>6660377</v>
+        <v>6660331</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4361,22 +4358,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124451081</v>
+        <v>124474451</v>
       </c>
       <c r="B35" t="n">
-        <v>57529</v>
+        <v>90445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4385,43 +4382,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>4189</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699683</v>
+        <v>699943</v>
       </c>
       <c r="R35" t="n">
-        <v>6660350</v>
+        <v>6660307</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4462,28 +4457,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124447694</v>
+        <v>124445043</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,38 +4492,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699777</v>
+        <v>699954</v>
       </c>
       <c r="R36" t="n">
-        <v>6660425</v>
+        <v>6660370</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4582,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124444974</v>
+        <v>124454215</v>
       </c>
       <c r="B37" t="n">
-        <v>5196</v>
+        <v>96979</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4598,42 +4603,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699954</v>
+        <v>699929</v>
       </c>
       <c r="R37" t="n">
-        <v>6660370</v>
+        <v>6660329</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124451595</v>
+        <v>124444956</v>
       </c>
       <c r="B38" t="n">
         <v>100279</v>
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R38" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124444956</v>
+        <v>124444867</v>
       </c>
       <c r="B39" t="n">
-        <v>100279</v>
+        <v>95455</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4807,24 +4807,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
@@ -4875,6 +4879,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4995,10 +5000,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124445043</v>
+        <v>124451595</v>
       </c>
       <c r="B41" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5011,39 +5016,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R41" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5102,10 +5102,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124454215</v>
+        <v>124447694</v>
       </c>
       <c r="B42" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5114,25 +5114,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5142,13 +5142,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699929</v>
+        <v>699777</v>
       </c>
       <c r="R42" t="n">
-        <v>6660329</v>
+        <v>6660425</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124452710</v>
+        <v>124474452</v>
       </c>
       <c r="B43" t="n">
         <v>100279</v>
@@ -5240,17 +5240,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699855</v>
+        <v>699807</v>
       </c>
       <c r="R43" t="n">
-        <v>6660145</v>
+        <v>6660377</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5294,22 +5294,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124445128</v>
+        <v>124452710</v>
       </c>
       <c r="B44" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699954</v>
+        <v>699855</v>
       </c>
       <c r="R44" t="n">
-        <v>6660370</v>
+        <v>6660145</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124444867</v>
+        <v>124449907</v>
       </c>
       <c r="B45" t="n">
-        <v>95455</v>
+        <v>57529</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5420,42 +5420,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699944</v>
+        <v>699754</v>
       </c>
       <c r="R45" t="n">
-        <v>6660374</v>
+        <v>6660376</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5496,7 +5497,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5515,10 +5515,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124447074</v>
+        <v>124450058</v>
       </c>
       <c r="B46" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5527,46 +5527,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699804</v>
+        <v>699808</v>
       </c>
       <c r="R46" t="n">
-        <v>6660392</v>
+        <v>6660347</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5622,10 +5617,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124446528</v>
+        <v>124451081</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,41 +5629,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699808</v>
+        <v>699683</v>
       </c>
       <c r="R47" t="n">
-        <v>6660347</v>
+        <v>6660350</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124450248</v>
+        <v>124447694</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,25 +3547,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699796</v>
+        <v>699777</v>
       </c>
       <c r="R27" t="n">
-        <v>6660315</v>
+        <v>6660425</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124445128</v>
+        <v>124446528</v>
       </c>
       <c r="B28" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3653,21 +3653,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699954</v>
+        <v>699808</v>
       </c>
       <c r="R28" t="n">
-        <v>6660370</v>
+        <v>6660347</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124446528</v>
+        <v>124451081</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,41 +3751,46 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699808</v>
+        <v>699683</v>
       </c>
       <c r="R29" t="n">
-        <v>6660347</v>
+        <v>6660350</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124474453</v>
+        <v>124447074</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3857,34 +3862,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699934</v>
+        <v>699804</v>
       </c>
       <c r="R30" t="n">
-        <v>6660275</v>
+        <v>6660392</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3931,22 +3941,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124447074</v>
+        <v>124451595</v>
       </c>
       <c r="B31" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,39 +3969,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699804</v>
+        <v>699683</v>
       </c>
       <c r="R31" t="n">
-        <v>6660392</v>
+        <v>6660350</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4050,10 +4055,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124444974</v>
+        <v>124444867</v>
       </c>
       <c r="B32" t="n">
-        <v>5196</v>
+        <v>95455</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4066,42 +4071,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699954</v>
+        <v>699944</v>
       </c>
       <c r="R32" t="n">
-        <v>6660370</v>
+        <v>6660374</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4139,6 +4143,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4157,10 +4162,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124444432</v>
+        <v>124450248</v>
       </c>
       <c r="B33" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4173,21 +4178,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4197,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699938</v>
+        <v>699796</v>
       </c>
       <c r="R33" t="n">
-        <v>6660298</v>
+        <v>6660315</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4259,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124451555</v>
+        <v>124474451</v>
       </c>
       <c r="B34" t="n">
-        <v>90448</v>
+        <v>90445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4271,20 +4276,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2008</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4292,26 +4297,20 @@
           <t>Pers.:Pers.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699672</v>
+        <v>699943</v>
       </c>
       <c r="R34" t="n">
-        <v>6660331</v>
+        <v>6660307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4352,28 +4351,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474451</v>
+        <v>124450058</v>
       </c>
       <c r="B35" t="n">
-        <v>90445</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4382,44 +4386,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4189</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699943</v>
+        <v>699808</v>
       </c>
       <c r="R35" t="n">
-        <v>6660307</v>
+        <v>6660347</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4457,33 +4458,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124445043</v>
+        <v>124451555</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>90448</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,31 +4488,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699954</v>
+        <v>699672</v>
       </c>
       <c r="R36" t="n">
-        <v>6660370</v>
+        <v>6660331</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124454215</v>
+        <v>124444974</v>
       </c>
       <c r="B37" t="n">
-        <v>96979</v>
+        <v>5196</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4603,37 +4603,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699929</v>
+        <v>699954</v>
       </c>
       <c r="R37" t="n">
-        <v>6660329</v>
+        <v>6660370</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4689,10 +4694,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124444956</v>
+        <v>124454215</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4705,21 +4710,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4729,10 +4734,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699944</v>
+        <v>699929</v>
       </c>
       <c r="R38" t="n">
-        <v>6660374</v>
+        <v>6660329</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4791,10 +4796,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124444867</v>
+        <v>124445128</v>
       </c>
       <c r="B39" t="n">
-        <v>95455</v>
+        <v>92326</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4807,41 +4812,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2818</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699944</v>
+        <v>699954</v>
       </c>
       <c r="R39" t="n">
-        <v>6660374</v>
+        <v>6660370</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4879,7 +4880,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124446732</v>
+        <v>124445043</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4910,38 +4910,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R40" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5000,7 +5005,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124451595</v>
+        <v>124474452</v>
       </c>
       <c r="B41" t="n">
         <v>100279</v>
@@ -5036,14 +5041,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699683</v>
+        <v>699807</v>
       </c>
       <c r="R41" t="n">
-        <v>6660350</v>
+        <v>6660377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5090,19 +5095,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124447694</v>
+        <v>124446732</v>
       </c>
       <c r="B42" t="n">
         <v>91012</v>
@@ -5142,10 +5147,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699777</v>
+        <v>699804</v>
       </c>
       <c r="R42" t="n">
-        <v>6660425</v>
+        <v>6660392</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5204,10 +5209,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124474452</v>
+        <v>124444432</v>
       </c>
       <c r="B43" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5220,37 +5225,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699807</v>
+        <v>699938</v>
       </c>
       <c r="R43" t="n">
-        <v>6660377</v>
+        <v>6660298</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5294,22 +5299,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124452710</v>
+        <v>124449907</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5318,38 +5323,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699855</v>
+        <v>699754</v>
       </c>
       <c r="R44" t="n">
-        <v>6660145</v>
+        <v>6660376</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5408,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124449907</v>
+        <v>124452710</v>
       </c>
       <c r="B45" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5420,43 +5430,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699754</v>
+        <v>699855</v>
       </c>
       <c r="R45" t="n">
-        <v>6660376</v>
+        <v>6660145</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5515,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124450058</v>
+        <v>124474453</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5527,41 +5532,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699808</v>
+        <v>699934</v>
       </c>
       <c r="R46" t="n">
-        <v>6660347</v>
+        <v>6660275</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5605,22 +5610,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124451081</v>
+        <v>124444956</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5629,46 +5634,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R47" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124447694</v>
+        <v>124447074</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,38 +3547,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699777</v>
+        <v>699804</v>
       </c>
       <c r="R27" t="n">
-        <v>6660425</v>
+        <v>6660392</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3637,10 +3642,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124446528</v>
+        <v>124447694</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,25 +3654,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,13 +3682,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699808</v>
+        <v>699777</v>
       </c>
       <c r="R28" t="n">
-        <v>6660347</v>
+        <v>6660425</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3739,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124451081</v>
+        <v>124446528</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,46 +3756,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699683</v>
+        <v>699808</v>
       </c>
       <c r="R29" t="n">
-        <v>6660350</v>
+        <v>6660347</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124447074</v>
+        <v>124451081</v>
       </c>
       <c r="B30" t="n">
-        <v>5176</v>
+        <v>57529</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,31 +3858,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699804</v>
+        <v>699683</v>
       </c>
       <c r="R30" t="n">
-        <v>6660392</v>
+        <v>6660350</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124444974</v>
+        <v>124454215</v>
       </c>
       <c r="B37" t="n">
-        <v>5196</v>
+        <v>96979</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4603,42 +4603,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699954</v>
+        <v>699929</v>
       </c>
       <c r="R37" t="n">
-        <v>6660370</v>
+        <v>6660329</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4694,10 +4689,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124454215</v>
+        <v>124444974</v>
       </c>
       <c r="B38" t="n">
-        <v>96979</v>
+        <v>5196</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4710,37 +4705,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699929</v>
+        <v>699954</v>
       </c>
       <c r="R38" t="n">
-        <v>6660329</v>
+        <v>6660370</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4898,10 +4898,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124445043</v>
+        <v>124474452</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4914,39 +4914,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699954</v>
+        <v>699807</v>
       </c>
       <c r="R40" t="n">
-        <v>6660370</v>
+        <v>6660377</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4993,22 +4988,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124474452</v>
+        <v>124445043</v>
       </c>
       <c r="B41" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5021,34 +5016,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699807</v>
+        <v>699954</v>
       </c>
       <c r="R41" t="n">
-        <v>6660377</v>
+        <v>6660370</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5095,12 +5095,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124447074</v>
+        <v>124447694</v>
       </c>
       <c r="B27" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,43 +3547,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699804</v>
+        <v>699777</v>
       </c>
       <c r="R27" t="n">
-        <v>6660392</v>
+        <v>6660425</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3642,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124447694</v>
+        <v>124451595</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3654,25 +3649,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3682,10 +3677,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699777</v>
+        <v>699683</v>
       </c>
       <c r="R28" t="n">
-        <v>6660425</v>
+        <v>6660350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3744,10 +3739,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124446528</v>
+        <v>124447074</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3760,37 +3755,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699808</v>
+        <v>699804</v>
       </c>
       <c r="R29" t="n">
-        <v>6660347</v>
+        <v>6660392</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124451081</v>
+        <v>124446528</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,46 +3858,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699683</v>
+        <v>699808</v>
       </c>
       <c r="R30" t="n">
-        <v>6660350</v>
+        <v>6660347</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3953,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124451595</v>
+        <v>124451081</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3965,28 +3960,33 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124447694</v>
+        <v>124451595</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,25 +3547,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699777</v>
+        <v>699683</v>
       </c>
       <c r="R27" t="n">
-        <v>6660425</v>
+        <v>6660350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124451595</v>
+        <v>124474453</v>
       </c>
       <c r="B28" t="n">
         <v>100279</v>
@@ -3673,14 +3673,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699683</v>
+        <v>699934</v>
       </c>
       <c r="R28" t="n">
-        <v>6660350</v>
+        <v>6660275</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,22 +3727,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124447074</v>
+        <v>124445128</v>
       </c>
       <c r="B29" t="n">
-        <v>5176</v>
+        <v>92326</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3755,39 +3755,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R29" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3846,10 +3841,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124446528</v>
+        <v>124444432</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,21 +3857,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699808</v>
+        <v>699938</v>
       </c>
       <c r="R30" t="n">
-        <v>6660347</v>
+        <v>6660298</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3948,10 +3943,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124451081</v>
+        <v>124450248</v>
       </c>
       <c r="B31" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3960,46 +3955,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699683</v>
+        <v>699796</v>
       </c>
       <c r="R31" t="n">
-        <v>6660350</v>
+        <v>6660315</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4055,10 +4045,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124444867</v>
+        <v>124445043</v>
       </c>
       <c r="B32" t="n">
-        <v>95455</v>
+        <v>5176</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4071,41 +4061,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699944</v>
+        <v>699954</v>
       </c>
       <c r="R32" t="n">
-        <v>6660374</v>
+        <v>6660370</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4143,7 +4134,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4162,7 +4152,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124450248</v>
+        <v>124444956</v>
       </c>
       <c r="B33" t="n">
         <v>100279</v>
@@ -4202,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699796</v>
+        <v>699944</v>
       </c>
       <c r="R33" t="n">
-        <v>6660315</v>
+        <v>6660374</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4264,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124474451</v>
+        <v>124451081</v>
       </c>
       <c r="B34" t="n">
-        <v>90445</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4276,41 +4266,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699943</v>
+        <v>699683</v>
       </c>
       <c r="R34" t="n">
-        <v>6660307</v>
+        <v>6660350</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4351,33 +4343,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124450058</v>
+        <v>124446528</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4386,25 +4373,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4476,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124451555</v>
+        <v>124450058</v>
       </c>
       <c r="B36" t="n">
-        <v>90448</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4492,46 +4479,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2008</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699672</v>
+        <v>699808</v>
       </c>
       <c r="R36" t="n">
-        <v>6660331</v>
+        <v>6660347</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4796,10 +4774,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124445128</v>
+        <v>124474451</v>
       </c>
       <c r="B39" t="n">
-        <v>92326</v>
+        <v>90445</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4812,34 +4790,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>4189</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699954</v>
+        <v>699943</v>
       </c>
       <c r="R39" t="n">
-        <v>6660370</v>
+        <v>6660307</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4880,25 +4861,30 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124474452</v>
+        <v>124452710</v>
       </c>
       <c r="B40" t="n">
         <v>100279</v>
@@ -4934,17 +4920,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699807</v>
+        <v>699855</v>
       </c>
       <c r="R40" t="n">
-        <v>6660377</v>
+        <v>6660145</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4988,22 +4974,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124445043</v>
+        <v>124444867</v>
       </c>
       <c r="B41" t="n">
-        <v>5176</v>
+        <v>95455</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,42 +5002,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699954</v>
+        <v>699944</v>
       </c>
       <c r="R41" t="n">
-        <v>6660370</v>
+        <v>6660374</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5089,6 +5074,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5107,10 +5093,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124446732</v>
+        <v>124474452</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5119,38 +5105,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699804</v>
+        <v>699807</v>
       </c>
       <c r="R42" t="n">
-        <v>6660392</v>
+        <v>6660377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5197,22 +5183,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124444432</v>
+        <v>124449907</v>
       </c>
       <c r="B43" t="n">
-        <v>92326</v>
+        <v>57529</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5221,38 +5207,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699938</v>
+        <v>699754</v>
       </c>
       <c r="R43" t="n">
-        <v>6660298</v>
+        <v>6660376</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5311,10 +5302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124449907</v>
+        <v>124447074</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>5176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5323,31 +5314,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5356,13 +5347,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699754</v>
+        <v>699804</v>
       </c>
       <c r="R44" t="n">
-        <v>6660376</v>
+        <v>6660392</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5418,10 +5409,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124452710</v>
+        <v>124447694</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5430,25 +5421,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5458,13 +5449,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699855</v>
+        <v>699777</v>
       </c>
       <c r="R45" t="n">
-        <v>6660145</v>
+        <v>6660425</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5520,10 +5511,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124474453</v>
+        <v>124451555</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5532,38 +5523,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699934</v>
+        <v>699672</v>
       </c>
       <c r="R46" t="n">
-        <v>6660275</v>
+        <v>6660331</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5610,22 +5610,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124444956</v>
+        <v>124446732</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,25 +5634,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5662,13 +5662,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699944</v>
+        <v>699804</v>
       </c>
       <c r="R47" t="n">
-        <v>6660374</v>
+        <v>6660392</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124451595</v>
+        <v>124454215</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3551,21 +3551,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699683</v>
+        <v>699929</v>
       </c>
       <c r="R27" t="n">
-        <v>6660350</v>
+        <v>6660329</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124474453</v>
+        <v>124450058</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,41 +3649,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699934</v>
+        <v>699808</v>
       </c>
       <c r="R28" t="n">
-        <v>6660275</v>
+        <v>6660347</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3727,22 +3727,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124445128</v>
+        <v>124451081</v>
       </c>
       <c r="B29" t="n">
-        <v>92326</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,38 +3751,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R29" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3841,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124444432</v>
+        <v>124451555</v>
       </c>
       <c r="B30" t="n">
-        <v>92326</v>
+        <v>90448</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3853,41 +3858,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>2008</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699938</v>
+        <v>699672</v>
       </c>
       <c r="R30" t="n">
-        <v>6660298</v>
+        <v>6660331</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3943,10 +3957,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124450248</v>
+        <v>124444974</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3959,37 +3973,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699796</v>
+        <v>699954</v>
       </c>
       <c r="R31" t="n">
-        <v>6660315</v>
+        <v>6660370</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4152,10 +4171,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124444956</v>
+        <v>124446732</v>
       </c>
       <c r="B33" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,25 +4183,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4192,13 +4211,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699944</v>
+        <v>699804</v>
       </c>
       <c r="R33" t="n">
-        <v>6660374</v>
+        <v>6660392</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124451081</v>
+        <v>124444956</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4266,46 +4285,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R34" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4361,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124446528</v>
+        <v>124444432</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4377,21 +4391,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4401,10 +4415,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699808</v>
+        <v>699938</v>
       </c>
       <c r="R35" t="n">
-        <v>6660347</v>
+        <v>6660298</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4463,10 +4477,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124450058</v>
+        <v>124450248</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4475,25 +4489,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4503,10 +4517,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699808</v>
+        <v>699796</v>
       </c>
       <c r="R36" t="n">
-        <v>6660347</v>
+        <v>6660315</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4565,10 +4579,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124454215</v>
+        <v>124474452</v>
       </c>
       <c r="B37" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4581,37 +4595,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699929</v>
+        <v>699807</v>
       </c>
       <c r="R37" t="n">
-        <v>6660329</v>
+        <v>6660377</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4655,22 +4669,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124444974</v>
+        <v>124447694</v>
       </c>
       <c r="B38" t="n">
-        <v>5196</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4679,43 +4693,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699954</v>
+        <v>699777</v>
       </c>
       <c r="R38" t="n">
-        <v>6660370</v>
+        <v>6660425</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4884,10 +4893,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124452710</v>
+        <v>124447074</v>
       </c>
       <c r="B40" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4900,37 +4909,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699855</v>
+        <v>699804</v>
       </c>
       <c r="R40" t="n">
-        <v>6660145</v>
+        <v>6660392</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4986,10 +5000,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124444867</v>
+        <v>124446528</v>
       </c>
       <c r="B41" t="n">
-        <v>95455</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5002,38 +5016,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2818</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699944</v>
+        <v>699808</v>
       </c>
       <c r="R41" t="n">
-        <v>6660374</v>
+        <v>6660347</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5074,7 +5084,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5093,7 +5102,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124474452</v>
+        <v>124474453</v>
       </c>
       <c r="B42" t="n">
         <v>100279</v>
@@ -5133,10 +5142,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699807</v>
+        <v>699934</v>
       </c>
       <c r="R42" t="n">
-        <v>6660377</v>
+        <v>6660275</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5295,17 +5304,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård, Viktor Lund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124447074</v>
+        <v>124444867</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>95455</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5318,42 +5327,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699804</v>
+        <v>699944</v>
       </c>
       <c r="R44" t="n">
-        <v>6660392</v>
+        <v>6660374</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5391,6 +5399,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5409,10 +5418,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124447694</v>
+        <v>124452710</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5421,25 +5430,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5449,13 +5458,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699777</v>
+        <v>699855</v>
       </c>
       <c r="R45" t="n">
-        <v>6660425</v>
+        <v>6660145</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5511,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124451555</v>
+        <v>124445128</v>
       </c>
       <c r="B46" t="n">
-        <v>90448</v>
+        <v>92326</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5523,47 +5532,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2008</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699672</v>
+        <v>699954</v>
       </c>
       <c r="R46" t="n">
-        <v>6660331</v>
+        <v>6660370</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5622,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124446732</v>
+        <v>124451595</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,25 +5634,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699804</v>
+        <v>699683</v>
       </c>
       <c r="R47" t="n">
-        <v>6660392</v>
+        <v>6660350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124454215</v>
+        <v>124450058</v>
       </c>
       <c r="B27" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,25 +3547,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699929</v>
+        <v>699808</v>
       </c>
       <c r="R27" t="n">
-        <v>6660329</v>
+        <v>6660347</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124450058</v>
+        <v>124444956</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,25 +3649,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699808</v>
+        <v>699944</v>
       </c>
       <c r="R28" t="n">
-        <v>6660347</v>
+        <v>6660374</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124451081</v>
+        <v>124444867</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>95455</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,46 +3751,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699683</v>
+        <v>699944</v>
       </c>
       <c r="R29" t="n">
-        <v>6660350</v>
+        <v>6660374</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3828,6 +3827,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124451555</v>
+        <v>124452710</v>
       </c>
       <c r="B30" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3858,50 +3858,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699672</v>
+        <v>699855</v>
       </c>
       <c r="R30" t="n">
-        <v>6660331</v>
+        <v>6660145</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3957,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124444974</v>
+        <v>124450248</v>
       </c>
       <c r="B31" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3973,42 +3964,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699954</v>
+        <v>699796</v>
       </c>
       <c r="R31" t="n">
-        <v>6660370</v>
+        <v>6660315</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4064,10 +4050,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124445043</v>
+        <v>124446528</v>
       </c>
       <c r="B32" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4080,42 +4066,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699954</v>
+        <v>699808</v>
       </c>
       <c r="R32" t="n">
-        <v>6660370</v>
+        <v>6660347</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4171,7 +4152,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124446732</v>
+        <v>124447694</v>
       </c>
       <c r="B33" t="n">
         <v>91012</v>
@@ -4211,10 +4192,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699804</v>
+        <v>699777</v>
       </c>
       <c r="R33" t="n">
-        <v>6660392</v>
+        <v>6660425</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4273,10 +4254,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124444956</v>
+        <v>124451081</v>
       </c>
       <c r="B34" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4285,41 +4266,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699944</v>
+        <v>699683</v>
       </c>
       <c r="R34" t="n">
-        <v>6660374</v>
+        <v>6660350</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4375,10 +4361,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124444432</v>
+        <v>124474451</v>
       </c>
       <c r="B35" t="n">
-        <v>92326</v>
+        <v>90445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,37 +4377,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>4189</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699938</v>
+        <v>699943</v>
       </c>
       <c r="R35" t="n">
-        <v>6660298</v>
+        <v>6660307</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4459,28 +4448,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124450248</v>
+        <v>124447074</v>
       </c>
       <c r="B36" t="n">
-        <v>100279</v>
+        <v>5176</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4493,37 +4487,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699796</v>
+        <v>699804</v>
       </c>
       <c r="R36" t="n">
-        <v>6660315</v>
+        <v>6660392</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4681,10 +4680,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124447694</v>
+        <v>124454215</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4693,25 +4692,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4721,13 +4720,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699777</v>
+        <v>699929</v>
       </c>
       <c r="R38" t="n">
-        <v>6660425</v>
+        <v>6660329</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4783,10 +4782,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124474451</v>
+        <v>124451595</v>
       </c>
       <c r="B39" t="n">
-        <v>90445</v>
+        <v>100279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4799,37 +4798,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4189</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699943</v>
+        <v>699683</v>
       </c>
       <c r="R39" t="n">
-        <v>6660307</v>
+        <v>6660350</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4870,33 +4866,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124447074</v>
+        <v>124451555</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>90448</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4905,31 +4896,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>2008</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4938,10 +4933,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699804</v>
+        <v>699672</v>
       </c>
       <c r="R40" t="n">
-        <v>6660392</v>
+        <v>6660331</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5000,10 +4995,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124446528</v>
+        <v>124444432</v>
       </c>
       <c r="B41" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,21 +5011,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699808</v>
+        <v>699938</v>
       </c>
       <c r="R41" t="n">
-        <v>6660347</v>
+        <v>6660298</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5102,10 +5097,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124474453</v>
+        <v>124445128</v>
       </c>
       <c r="B42" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5118,34 +5113,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699934</v>
+        <v>699954</v>
       </c>
       <c r="R42" t="n">
-        <v>6660275</v>
+        <v>6660370</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5192,22 +5187,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124449907</v>
+        <v>124445043</v>
       </c>
       <c r="B43" t="n">
-        <v>57529</v>
+        <v>5176</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5216,31 +5211,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5249,13 +5244,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699754</v>
+        <v>699954</v>
       </c>
       <c r="R43" t="n">
-        <v>6660376</v>
+        <v>6660370</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5304,17 +5299,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Martin Axegård, Viktor Lund</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124444867</v>
+        <v>124449907</v>
       </c>
       <c r="B44" t="n">
-        <v>95455</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5323,42 +5318,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699944</v>
+        <v>699754</v>
       </c>
       <c r="R44" t="n">
-        <v>6660374</v>
+        <v>6660376</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5399,7 +5395,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5418,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124452710</v>
+        <v>124444974</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5434,37 +5429,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699855</v>
+        <v>699954</v>
       </c>
       <c r="R45" t="n">
-        <v>6660145</v>
+        <v>6660370</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124445128</v>
+        <v>124474453</v>
       </c>
       <c r="B46" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5536,34 +5536,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699954</v>
+        <v>699934</v>
       </c>
       <c r="R46" t="n">
-        <v>6660370</v>
+        <v>6660275</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5610,22 +5610,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124451595</v>
+        <v>124446732</v>
       </c>
       <c r="B47" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5634,25 +5634,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5662,10 +5662,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699683</v>
+        <v>699804</v>
       </c>
       <c r="R47" t="n">
-        <v>6660350</v>
+        <v>6660392</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124450058</v>
+        <v>124474452</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>100279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3547,41 +3547,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699808</v>
+        <v>699807</v>
       </c>
       <c r="R27" t="n">
-        <v>6660347</v>
+        <v>6660377</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3625,22 +3625,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124444956</v>
+        <v>124447694</v>
       </c>
       <c r="B28" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,25 +3649,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3677,13 +3677,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699944</v>
+        <v>699777</v>
       </c>
       <c r="R28" t="n">
-        <v>6660374</v>
+        <v>6660425</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3739,10 +3739,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124444867</v>
+        <v>124449907</v>
       </c>
       <c r="B29" t="n">
-        <v>95455</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,42 +3751,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699944</v>
+        <v>699754</v>
       </c>
       <c r="R29" t="n">
-        <v>6660374</v>
+        <v>6660376</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3827,7 +3828,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3846,10 +3846,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124452710</v>
+        <v>124444867</v>
       </c>
       <c r="B30" t="n">
-        <v>100279</v>
+        <v>95455</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,34 +3862,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699855</v>
+        <v>699944</v>
       </c>
       <c r="R30" t="n">
-        <v>6660145</v>
+        <v>6660374</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3930,6 +3934,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3948,10 +3953,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124450248</v>
+        <v>124474451</v>
       </c>
       <c r="B31" t="n">
-        <v>100279</v>
+        <v>90445</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3964,37 +3969,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699796</v>
+        <v>699943</v>
       </c>
       <c r="R31" t="n">
-        <v>6660315</v>
+        <v>6660307</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4032,28 +4040,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124446528</v>
+        <v>124446732</v>
       </c>
       <c r="B32" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4062,25 +4075,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4090,13 +4103,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699808</v>
+        <v>699804</v>
       </c>
       <c r="R32" t="n">
-        <v>6660347</v>
+        <v>6660392</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4152,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124447694</v>
+        <v>124447074</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4164,38 +4177,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699777</v>
+        <v>699804</v>
       </c>
       <c r="R33" t="n">
-        <v>6660425</v>
+        <v>6660392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4254,10 +4272,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124451081</v>
+        <v>124450058</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4270,42 +4288,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699683</v>
+        <v>699808</v>
       </c>
       <c r="R34" t="n">
-        <v>6660350</v>
+        <v>6660347</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4361,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124474451</v>
+        <v>124445043</v>
       </c>
       <c r="B35" t="n">
-        <v>90445</v>
+        <v>5176</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4377,37 +4390,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4189</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699943</v>
+        <v>699954</v>
       </c>
       <c r="R35" t="n">
-        <v>6660307</v>
+        <v>6660370</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4448,33 +4463,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124447074</v>
+        <v>124450248</v>
       </c>
       <c r="B36" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4487,42 +4497,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699804</v>
+        <v>699796</v>
       </c>
       <c r="R36" t="n">
-        <v>6660392</v>
+        <v>6660315</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4578,7 +4583,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124474452</v>
+        <v>124474453</v>
       </c>
       <c r="B37" t="n">
         <v>100279</v>
@@ -4618,10 +4623,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699807</v>
+        <v>699934</v>
       </c>
       <c r="R37" t="n">
-        <v>6660377</v>
+        <v>6660275</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4680,10 +4685,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124454215</v>
+        <v>124451595</v>
       </c>
       <c r="B38" t="n">
-        <v>96979</v>
+        <v>100279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4696,21 +4701,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4720,13 +4725,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699929</v>
+        <v>699683</v>
       </c>
       <c r="R38" t="n">
-        <v>6660329</v>
+        <v>6660350</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,10 +4787,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124451595</v>
+        <v>124444974</v>
       </c>
       <c r="B39" t="n">
-        <v>100279</v>
+        <v>5196</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4798,34 +4803,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699683</v>
+        <v>699954</v>
       </c>
       <c r="R39" t="n">
-        <v>6660350</v>
+        <v>6660370</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4884,10 +4894,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124451555</v>
+        <v>124446528</v>
       </c>
       <c r="B40" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4896,50 +4906,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699672</v>
+        <v>699808</v>
       </c>
       <c r="R40" t="n">
-        <v>6660331</v>
+        <v>6660347</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4995,10 +4996,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124444432</v>
+        <v>124452710</v>
       </c>
       <c r="B41" t="n">
-        <v>92326</v>
+        <v>100279</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5011,21 +5012,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5035,10 +5036,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699938</v>
+        <v>699855</v>
       </c>
       <c r="R41" t="n">
-        <v>6660298</v>
+        <v>6660145</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5097,10 +5098,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124445128</v>
+        <v>124454215</v>
       </c>
       <c r="B42" t="n">
-        <v>92326</v>
+        <v>96979</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5113,21 +5114,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5137,13 +5138,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699954</v>
+        <v>699929</v>
       </c>
       <c r="R42" t="n">
-        <v>6660370</v>
+        <v>6660329</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5199,10 +5200,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124445043</v>
+        <v>124444432</v>
       </c>
       <c r="B43" t="n">
-        <v>5176</v>
+        <v>92326</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5215,42 +5216,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699954</v>
+        <v>699938</v>
       </c>
       <c r="R43" t="n">
-        <v>6660370</v>
+        <v>6660298</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5306,10 +5302,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124449907</v>
+        <v>124444956</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5318,43 +5314,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699754</v>
+        <v>699944</v>
       </c>
       <c r="R44" t="n">
-        <v>6660376</v>
+        <v>6660374</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5413,10 +5404,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124444974</v>
+        <v>124451555</v>
       </c>
       <c r="B45" t="n">
-        <v>5196</v>
+        <v>90448</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5425,31 +5416,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>2008</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5458,10 +5453,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699954</v>
+        <v>699672</v>
       </c>
       <c r="R45" t="n">
-        <v>6660370</v>
+        <v>6660331</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5520,10 +5515,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124474453</v>
+        <v>124445128</v>
       </c>
       <c r="B46" t="n">
-        <v>100279</v>
+        <v>92326</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5536,34 +5531,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699934</v>
+        <v>699954</v>
       </c>
       <c r="R46" t="n">
-        <v>6660275</v>
+        <v>6660370</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5610,22 +5605,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124446732</v>
+        <v>124451081</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5638,34 +5633,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699804</v>
+        <v>699683</v>
       </c>
       <c r="R47" t="n">
-        <v>6660392</v>
+        <v>6660350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -3535,7 +3535,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124474452</v>
+        <v>124452710</v>
       </c>
       <c r="B27" t="n">
         <v>100279</v>
@@ -3571,17 +3571,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699807</v>
+        <v>699855</v>
       </c>
       <c r="R27" t="n">
-        <v>6660377</v>
+        <v>6660145</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3625,22 +3625,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124447694</v>
+        <v>124444867</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>95455</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3649,41 +3649,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699777</v>
+        <v>699944</v>
       </c>
       <c r="R28" t="n">
-        <v>6660425</v>
+        <v>6660374</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3721,6 +3725,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3739,10 +3744,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124449907</v>
+        <v>124474453</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>100279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3751,46 +3756,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699754</v>
+        <v>699934</v>
       </c>
       <c r="R29" t="n">
-        <v>6660376</v>
+        <v>6660275</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3834,22 +3834,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124444867</v>
+        <v>124444432</v>
       </c>
       <c r="B30" t="n">
-        <v>95455</v>
+        <v>92326</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,38 +3862,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2818</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699944</v>
+        <v>699938</v>
       </c>
       <c r="R30" t="n">
-        <v>6660374</v>
+        <v>6660298</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3934,7 +3930,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3953,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124474451</v>
+        <v>124447074</v>
       </c>
       <c r="B31" t="n">
-        <v>90445</v>
+        <v>5176</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,37 +3964,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4189</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699943</v>
+        <v>699804</v>
       </c>
       <c r="R31" t="n">
-        <v>6660307</v>
+        <v>6660392</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4040,30 +4037,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124446732</v>
+        <v>124447694</v>
       </c>
       <c r="B32" t="n">
         <v>91012</v>
@@ -4103,10 +4095,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699804</v>
+        <v>699777</v>
       </c>
       <c r="R32" t="n">
-        <v>6660392</v>
+        <v>6660425</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4165,10 +4157,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124447074</v>
+        <v>124444974</v>
       </c>
       <c r="B33" t="n">
-        <v>5176</v>
+        <v>5196</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,27 +4173,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4210,10 +4202,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699804</v>
+        <v>699954</v>
       </c>
       <c r="R33" t="n">
-        <v>6660392</v>
+        <v>6660370</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4272,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124450058</v>
+        <v>124474451</v>
       </c>
       <c r="B34" t="n">
-        <v>91012</v>
+        <v>90445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4284,41 +4276,44 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>4189</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699808</v>
+        <v>699943</v>
       </c>
       <c r="R34" t="n">
-        <v>6660347</v>
+        <v>6660307</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4356,28 +4351,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124445043</v>
+        <v>124450248</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>100279</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4390,42 +4390,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699954</v>
+        <v>699796</v>
       </c>
       <c r="R35" t="n">
-        <v>6660370</v>
+        <v>6660315</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4481,10 +4476,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124450248</v>
+        <v>124451555</v>
       </c>
       <c r="B36" t="n">
-        <v>100279</v>
+        <v>90448</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4493,41 +4488,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>2008</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699796</v>
+        <v>699672</v>
       </c>
       <c r="R36" t="n">
-        <v>6660315</v>
+        <v>6660331</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4583,10 +4587,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124474453</v>
+        <v>124454215</v>
       </c>
       <c r="B37" t="n">
-        <v>100279</v>
+        <v>96979</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4599,37 +4603,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699934</v>
+        <v>699929</v>
       </c>
       <c r="R37" t="n">
-        <v>6660275</v>
+        <v>6660329</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4673,19 +4677,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124451595</v>
+        <v>124474452</v>
       </c>
       <c r="B38" t="n">
         <v>100279</v>
@@ -4721,14 +4725,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699683</v>
+        <v>699807</v>
       </c>
       <c r="R38" t="n">
-        <v>6660350</v>
+        <v>6660377</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4775,22 +4779,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124444974</v>
+        <v>124451595</v>
       </c>
       <c r="B39" t="n">
-        <v>5196</v>
+        <v>100279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4803,39 +4807,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699954</v>
+        <v>699683</v>
       </c>
       <c r="R39" t="n">
-        <v>6660370</v>
+        <v>6660350</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4996,10 +4995,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124452710</v>
+        <v>124451081</v>
       </c>
       <c r="B41" t="n">
-        <v>100279</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5008,41 +5007,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699855</v>
+        <v>699683</v>
       </c>
       <c r="R41" t="n">
-        <v>6660145</v>
+        <v>6660350</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5098,10 +5102,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124454215</v>
+        <v>124445128</v>
       </c>
       <c r="B42" t="n">
-        <v>96979</v>
+        <v>92326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5114,21 +5118,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5138,13 +5142,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699929</v>
+        <v>699954</v>
       </c>
       <c r="R42" t="n">
-        <v>6660329</v>
+        <v>6660370</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5200,10 +5204,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124444432</v>
+        <v>124445043</v>
       </c>
       <c r="B43" t="n">
-        <v>92326</v>
+        <v>5176</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5216,37 +5220,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699938</v>
+        <v>699954</v>
       </c>
       <c r="R43" t="n">
-        <v>6660298</v>
+        <v>6660370</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124444956</v>
+        <v>124450058</v>
       </c>
       <c r="B44" t="n">
-        <v>100279</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5314,25 +5323,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5342,10 +5351,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699944</v>
+        <v>699808</v>
       </c>
       <c r="R44" t="n">
-        <v>6660374</v>
+        <v>6660347</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5404,10 +5413,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124451555</v>
+        <v>124444956</v>
       </c>
       <c r="B45" t="n">
-        <v>90448</v>
+        <v>100279</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5416,50 +5425,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2008</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699672</v>
+        <v>699944</v>
       </c>
       <c r="R45" t="n">
-        <v>6660331</v>
+        <v>6660374</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5515,10 +5515,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124445128</v>
+        <v>124449907</v>
       </c>
       <c r="B46" t="n">
-        <v>92326</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5527,41 +5527,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699954</v>
+        <v>699754</v>
       </c>
       <c r="R46" t="n">
-        <v>6660370</v>
+        <v>6660376</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5617,10 +5622,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124451081</v>
+        <v>124446732</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5633,39 +5638,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699683</v>
+        <v>699804</v>
       </c>
       <c r="R47" t="n">
-        <v>6660350</v>
+        <v>6660392</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5727,7 +5727,7 @@
         <v>124447516</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5727,12 +5727,7 @@
         <v>124447516</v>
       </c>
       <c r="B48" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5828,6 +5828,2346 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128760320</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91001</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>699820</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6660298</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128760312</v>
+      </c>
+      <c r="B50" t="n">
+        <v>92790</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>699945</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6660298</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128760336</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86956</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>699835</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6660288</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128760333</v>
+      </c>
+      <c r="B52" t="n">
+        <v>86949</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>449</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>699668</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6660391</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128760316</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91239</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>699935</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6660294</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128760321</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92745</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>150</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>699817</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6660321</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128760327</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92748</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>699826</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6660373</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128760313</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>699942</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6660292</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128760328</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92745</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>150</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>699826</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6660389</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128760323</v>
+      </c>
+      <c r="B58" t="n">
+        <v>86984</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>433</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Duvspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>699814</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6660362</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128760322</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90964</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>699806</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6660365</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128760317</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92764</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>699904</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6660284</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128760329</v>
+      </c>
+      <c r="B61" t="n">
+        <v>92764</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>699825</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6660385</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128760311</v>
+      </c>
+      <c r="B62" t="n">
+        <v>86729</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>699951</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6660298</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128760331</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92766</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>789</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Raggtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum mirabile</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>699784</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6660411</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128760337</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92764</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>699843</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6660300</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128760324</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92745</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>150</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>699814</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6660360</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128760326</v>
+      </c>
+      <c r="B66" t="n">
+        <v>92745</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>150</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>699824</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6660374</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128760334</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92460</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>699664</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6660365</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128760310</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90927</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>699951</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6660295</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128760330</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92764</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>699803</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6660408</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128760332</v>
+      </c>
+      <c r="B70" t="n">
+        <v>92220</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>699706</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6660389</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128760318</v>
+      </c>
+      <c r="B71" t="n">
+        <v>92764</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2058</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Koppartaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnellum lundellii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>699868</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6660289</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128760325</v>
+      </c>
+      <c r="B72" t="n">
+        <v>92758</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>788</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>699827</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6660373</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91239</v>
+        <v>91240</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>90964</v>
+        <v>90965</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92766</v>
+        <v>92767</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90927</v>
+        <v>90928</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92220</v>
+        <v>92221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91240</v>
+        <v>91267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>86984</v>
+        <v>87011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>90965</v>
+        <v>90992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92767</v>
+        <v>92794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92461</v>
+        <v>92488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92221</v>
+        <v>92248</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91029</v>
+        <v>91034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91267</v>
+        <v>91272</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87011</v>
+        <v>87015</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>90992</v>
+        <v>90997</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92488</v>
+        <v>92493</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92248</v>
+        <v>92253</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92786</v>
+        <v>92791</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91034</v>
+        <v>91039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>86987</v>
+        <v>86988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>86980</v>
+        <v>86981</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91272</v>
+        <v>91277</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87015</v>
+        <v>87016</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>90997</v>
+        <v>91002</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92799</v>
+        <v>92804</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92493</v>
+        <v>92498</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92253</v>
+        <v>92258</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92791</v>
+        <v>92796</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91039</v>
+        <v>91043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>86988</v>
+        <v>86992</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91277</v>
+        <v>91281</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87016</v>
+        <v>87020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>91002</v>
+        <v>91006</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92804</v>
+        <v>92808</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92498</v>
+        <v>92502</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92258</v>
+        <v>92262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92796</v>
+        <v>92800</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91043</v>
+        <v>91048</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>86992</v>
+        <v>86997</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91281</v>
+        <v>91286</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87020</v>
+        <v>87025</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>91006</v>
+        <v>91011</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92808</v>
+        <v>92813</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92262</v>
+        <v>92267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91055</v>
+        <v>91058</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>87004</v>
+        <v>87007</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91293</v>
+        <v>91296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92803</v>
+        <v>92808</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87032</v>
+        <v>87035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>91018</v>
+        <v>91021</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92821</v>
+        <v>92826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92515</v>
+        <v>92520</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92275</v>
+        <v>92280</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92819</v>
+        <v>92824</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92813</v>
+        <v>92818</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91058</v>
+        <v>91061</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>87007</v>
+        <v>87010</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91296</v>
+        <v>91299</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92808</v>
+        <v>92811</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87035</v>
+        <v>87038</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>91021</v>
+        <v>91024</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92826</v>
+        <v>92829</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92520</v>
+        <v>92523</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90984</v>
+        <v>90987</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92280</v>
+        <v>92283</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92824</v>
+        <v>92827</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91061</v>
+        <v>91065</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>87010</v>
+        <v>87014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91299</v>
+        <v>91305</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87038</v>
+        <v>87042</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>91024</v>
+        <v>91028</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92829</v>
+        <v>92836</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92523</v>
+        <v>92530</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90987</v>
+        <v>90991</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92283</v>
+        <v>92290</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92827</v>
+        <v>92834</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92821</v>
+        <v>92828</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -5833,7 +5833,7 @@
         <v>128760320</v>
       </c>
       <c r="B49" t="n">
-        <v>91065</v>
+        <v>91074</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>128760312</v>
       </c>
       <c r="B50" t="n">
-        <v>92862</v>
+        <v>92871</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6027,7 +6027,7 @@
         <v>128760336</v>
       </c>
       <c r="B51" t="n">
-        <v>87014</v>
+        <v>87023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>128760333</v>
       </c>
       <c r="B52" t="n">
-        <v>87007</v>
+        <v>87016</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128760316</v>
       </c>
       <c r="B53" t="n">
-        <v>91305</v>
+        <v>91314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128760321</v>
       </c>
       <c r="B54" t="n">
-        <v>92815</v>
+        <v>92824</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128760327</v>
       </c>
       <c r="B55" t="n">
-        <v>92818</v>
+        <v>92827</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128760313</v>
       </c>
       <c r="B56" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128760328</v>
       </c>
       <c r="B57" t="n">
-        <v>92815</v>
+        <v>92824</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128760323</v>
       </c>
       <c r="B58" t="n">
-        <v>87042</v>
+        <v>87051</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>128760322</v>
       </c>
       <c r="B59" t="n">
-        <v>91028</v>
+        <v>91037</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>128760317</v>
       </c>
       <c r="B60" t="n">
-        <v>92834</v>
+        <v>92843</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128760329</v>
       </c>
       <c r="B61" t="n">
-        <v>92834</v>
+        <v>92843</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128760311</v>
       </c>
       <c r="B62" t="n">
-        <v>86786</v>
+        <v>86795</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128760331</v>
       </c>
       <c r="B63" t="n">
-        <v>92836</v>
+        <v>92845</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>128760337</v>
       </c>
       <c r="B64" t="n">
-        <v>92834</v>
+        <v>92843</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>128760324</v>
       </c>
       <c r="B65" t="n">
-        <v>92815</v>
+        <v>92824</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>128760326</v>
       </c>
       <c r="B66" t="n">
-        <v>92815</v>
+        <v>92824</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>128760334</v>
       </c>
       <c r="B67" t="n">
-        <v>92530</v>
+        <v>92539</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>128760310</v>
       </c>
       <c r="B68" t="n">
-        <v>90991</v>
+        <v>91000</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
         <v>128760330</v>
       </c>
       <c r="B69" t="n">
-        <v>92834</v>
+        <v>92843</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>128760332</v>
       </c>
       <c r="B70" t="n">
-        <v>92290</v>
+        <v>92299</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>128760318</v>
       </c>
       <c r="B71" t="n">
-        <v>92834</v>
+        <v>92843</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>128760325</v>
       </c>
       <c r="B72" t="n">
-        <v>92828</v>
+        <v>92837</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2960,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
@@ -8168,6 +8168,321 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>130379971</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>699710</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6660225</v>
+      </c>
+      <c r="S73" t="n">
+        <v>50</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>130379975</v>
+      </c>
+      <c r="B74" t="n">
+        <v>93022</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>699783</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6660083</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>130379973</v>
+      </c>
+      <c r="B75" t="n">
+        <v>86979</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>699820</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6660145</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93022</v>
+        <v>93025</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>86979</v>
+        <v>86982</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8173,7 +8173,7 @@
         <v>130379971</v>
       </c>
       <c r="B73" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93025</v>
+        <v>93051</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>86982</v>
+        <v>87008</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93051</v>
+        <v>93052</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>87008</v>
+        <v>87009</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>87009</v>
+        <v>87010</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8173,7 +8173,7 @@
         <v>130379971</v>
       </c>
       <c r="B73" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>87010</v>
+        <v>87012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93055</v>
+        <v>93059</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8173,7 +8173,7 @@
         <v>130379971</v>
       </c>
       <c r="B73" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93059</v>
+        <v>93072</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>87012</v>
+        <v>87021</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8173,7 +8173,7 @@
         <v>130379971</v>
       </c>
       <c r="B73" t="n">
-        <v>57859</v>
+        <v>57860</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93072</v>
+        <v>93073</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>87021</v>
+        <v>87022</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -8173,7 +8173,7 @@
         <v>130379971</v>
       </c>
       <c r="B73" t="n">
-        <v>57860</v>
+        <v>57861</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>130379975</v>
       </c>
       <c r="B74" t="n">
-        <v>93073</v>
+        <v>93074</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>130379973</v>
       </c>
       <c r="B75" t="n">
-        <v>87022</v>
+        <v>87023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82416820</v>
+        <v>82416823</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>699837.6204890078</v>
+        <v>699838</v>
       </c>
       <c r="R2" t="n">
-        <v>6660370.881627454</v>
+        <v>6660371</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -751,19 +746,9 @@
           <t>2019-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,56 +780,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82416822</v>
+        <v>112662576</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>699837.6204890078</v>
+        <v>699809</v>
       </c>
       <c r="R3" t="n">
-        <v>6660370.881627454</v>
+        <v>6660356</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +882,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -915,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82416821</v>
+        <v>128760321</v>
       </c>
       <c r="B4" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,40 +904,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2058</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>699837.6204890078</v>
+        <v>699817</v>
       </c>
       <c r="R4" t="n">
-        <v>6660370.881627454</v>
+        <v>6660321</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +958,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,79 +972,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82416824</v>
+        <v>128760324</v>
       </c>
       <c r="B5" t="n">
-        <v>85261</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättespindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius praestans</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Cordier) Gillet</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>699837.6204890078</v>
+        <v>699814</v>
       </c>
       <c r="R5" t="n">
-        <v>6660370.881627454</v>
+        <v>6660360</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,22 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,79 +1069,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82416825</v>
+        <v>128760326</v>
       </c>
       <c r="B6" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3674</v>
+        <v>150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>699837.6204890078</v>
+        <v>699824</v>
       </c>
       <c r="R6" t="n">
-        <v>6660370.881627454</v>
+        <v>6660374</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,22 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,79 +1166,66 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82416827</v>
+        <v>128760328</v>
       </c>
       <c r="B7" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3762</v>
+        <v>150</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>699837.6204890078</v>
+        <v>699826</v>
       </c>
       <c r="R7" t="n">
-        <v>6660370.881627454</v>
+        <v>6660389</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,22 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,79 +1263,78 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82416818</v>
+        <v>124445502</v>
       </c>
       <c r="B8" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1968</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>699837.6204890078</v>
+        <v>699912</v>
       </c>
       <c r="R8" t="n">
-        <v>6660370.881627454</v>
+        <v>6660398</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,22 +1358,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,31 +1379,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82416823</v>
+        <v>128760323</v>
       </c>
       <c r="B9" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87403</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,40 +1402,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>433</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Duvspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
+          <t>Cortinarius caesiocanescens s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lundås, Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>699837.6204890078</v>
+        <v>699814</v>
       </c>
       <c r="R9" t="n">
-        <v>6660370.881627454</v>
+        <v>6660362</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,22 +1452,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,73 +1466,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105298090</v>
+        <v>128760333</v>
       </c>
       <c r="B10" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>223246</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>699720.7897451062</v>
+        <v>699668</v>
       </c>
       <c r="R10" t="n">
-        <v>6660259.385753377</v>
+        <v>6660391</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,27 +1553,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,65 +1573,63 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105298081</v>
+        <v>82416824</v>
       </c>
       <c r="B11" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223246</v>
+        <v>460</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Jättespindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cortinarius praestans</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Cordier) Gillet</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>699636.3727569948</v>
+        <v>699838</v>
       </c>
       <c r="R11" t="n">
-        <v>6660447.081050741</v>
+        <v>6660371</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,27 +1653,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ungt träd</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,33 +1667,33 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112662494</v>
+        <v>128760325</v>
       </c>
       <c r="B12" t="n">
-        <v>91040</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,40 +1701,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2058</v>
+        <v>788</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>699752</v>
+        <v>699827</v>
       </c>
       <c r="R12" t="n">
-        <v>6660343</v>
+        <v>6660373</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,12 +1755,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,79 +1769,70 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112662525</v>
+        <v>128760331</v>
       </c>
       <c r="B13" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3674</v>
+        <v>789</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>699802</v>
+        <v>699784</v>
       </c>
       <c r="R13" t="n">
-        <v>6660244</v>
+        <v>6660411</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2052,12 +1856,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,38 +1870,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112662567</v>
+        <v>124446732</v>
       </c>
       <c r="B14" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,40 +1899,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>699809</v>
+        <v>699804</v>
       </c>
       <c r="R14" t="n">
-        <v>6660356</v>
+        <v>6660392</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,12 +1953,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,79 +1967,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112662568</v>
+        <v>124447694</v>
       </c>
       <c r="B15" t="n">
-        <v>91044</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>699809</v>
+        <v>699777</v>
       </c>
       <c r="R15" t="n">
-        <v>6660356</v>
+        <v>6660425</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2272,12 +2050,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,87 +2064,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112662596</v>
+        <v>124450058</v>
       </c>
       <c r="B16" t="n">
-        <v>91040</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2058</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>699809</v>
+        <v>699808</v>
       </c>
       <c r="R16" t="n">
-        <v>6660356</v>
+        <v>6660347</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2390,12 +2147,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,60 +2161,50 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112662544</v>
+        <v>82416818</v>
       </c>
       <c r="B17" t="n">
-        <v>89322</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2466,17 +2213,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699829</v>
+        <v>699838</v>
       </c>
       <c r="R17" t="n">
-        <v>6660299</v>
+        <v>6660371</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2500,12 +2247,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,7 +2273,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2537,56 +2284,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112662570</v>
+        <v>124451555</v>
       </c>
       <c r="B18" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4363</v>
+        <v>2008</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699809</v>
+        <v>699672</v>
       </c>
       <c r="R18" t="n">
-        <v>6660356</v>
+        <v>6660331</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2610,12 +2358,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,87 +2372,69 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112662576</v>
+        <v>82416821</v>
       </c>
       <c r="B19" t="n">
-        <v>91021</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>150</v>
+        <v>2058</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699809</v>
+        <v>699838</v>
       </c>
       <c r="R19" t="n">
-        <v>6660356</v>
+        <v>6660371</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2728,12 +2458,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,7 +2484,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2765,37 +2495,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112662602</v>
+        <v>112662494</v>
       </c>
       <c r="B20" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>2058</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2808,13 +2533,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699809</v>
+        <v>699752</v>
       </c>
       <c r="R20" t="n">
-        <v>6660356</v>
+        <v>6660342</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2875,41 +2600,44 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112662497</v>
+        <v>112662596</v>
       </c>
       <c r="B21" t="n">
-        <v>89314</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5733</v>
+        <v>2058</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Såpfingersvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria lutea</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vent.) Schild</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2918,13 +2646,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699752</v>
+        <v>699809</v>
       </c>
       <c r="R21" t="n">
-        <v>6660343</v>
+        <v>6660356</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2960,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
@@ -2985,56 +2713,52 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112662498</v>
+        <v>128760317</v>
       </c>
       <c r="B22" t="n">
-        <v>85434</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>2058</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699752</v>
+        <v>699904</v>
       </c>
       <c r="R22" t="n">
-        <v>6660343</v>
+        <v>6660284</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3058,12 +2782,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,79 +2796,70 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112662524</v>
+        <v>128760318</v>
       </c>
       <c r="B23" t="n">
-        <v>90505</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>232138</v>
+        <v>2058</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Ryman</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699802</v>
+        <v>699868</v>
       </c>
       <c r="R23" t="n">
-        <v>6660244</v>
+        <v>6660289</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,12 +2883,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,79 +2897,66 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112662501</v>
+        <v>128760329</v>
       </c>
       <c r="B24" t="n">
-        <v>91024</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>2058</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699752</v>
+        <v>699825</v>
       </c>
       <c r="R24" t="n">
-        <v>6660343</v>
+        <v>6660385</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3278,12 +2980,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3292,79 +2994,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112662546</v>
+        <v>128760330</v>
       </c>
       <c r="B25" t="n">
-        <v>85598</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3674</v>
+        <v>2058</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699829</v>
+        <v>699803</v>
       </c>
       <c r="R25" t="n">
-        <v>6660299</v>
+        <v>6660408</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3388,12 +3077,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,79 +3091,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112662551</v>
+        <v>128760337</v>
       </c>
       <c r="B26" t="n">
-        <v>85555</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3624</v>
+        <v>2058</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699829</v>
+        <v>699843</v>
       </c>
       <c r="R26" t="n">
-        <v>6660299</v>
+        <v>6660300</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,12 +3174,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3512,38 +3188,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124452710</v>
+        <v>124444867</v>
       </c>
       <c r="B27" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3551,34 +3217,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699855</v>
+        <v>699944</v>
       </c>
       <c r="R27" t="n">
-        <v>6660145</v>
+        <v>6660374</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3619,6 +3289,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3637,15 +3308,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124444867</v>
+        <v>128760316</v>
       </c>
       <c r="B28" t="n">
-        <v>95455</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3653,41 +3319,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2818</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699944</v>
+        <v>699935</v>
       </c>
       <c r="R28" t="n">
-        <v>6660374</v>
+        <v>6660294</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3711,12 +3373,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3725,56 +3387,50 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124474453</v>
+        <v>128760310</v>
       </c>
       <c r="B29" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>3286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3784,10 +3440,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699934</v>
+        <v>699951</v>
       </c>
       <c r="R29" t="n">
-        <v>6660275</v>
+        <v>6660295</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,12 +3470,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3834,27 +3490,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124444432</v>
+        <v>112662551</v>
       </c>
       <c r="B30" t="n">
-        <v>92326</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3862,37 +3513,36 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>3624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699938</v>
+        <v>699830</v>
       </c>
       <c r="R30" t="n">
         <v>6660298</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3916,12 +3566,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,33 +3580,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124447074</v>
+        <v>82416825</v>
       </c>
       <c r="B31" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3964,42 +3614,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>3674</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699804</v>
+        <v>699838</v>
       </c>
       <c r="R31" t="n">
-        <v>6660392</v>
+        <v>6660371</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4023,12 +3671,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,71 +3685,74 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124447694</v>
+        <v>112662525</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>3674</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699777</v>
+        <v>699802</v>
       </c>
       <c r="R32" t="n">
-        <v>6660425</v>
+        <v>6660244</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4125,12 +3776,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4139,33 +3790,33 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124444974</v>
+        <v>112662546</v>
       </c>
       <c r="B33" t="n">
-        <v>5196</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4173,42 +3824,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>3674</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699954</v>
+        <v>699830</v>
       </c>
       <c r="R33" t="n">
-        <v>6660370</v>
+        <v>6660298</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4232,12 +3881,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4246,33 +3895,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124474451</v>
+        <v>112662602</v>
       </c>
       <c r="B34" t="n">
-        <v>90445</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4280,21 +3929,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4189</v>
+        <v>3674</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4307,13 +3956,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699943</v>
+        <v>699809</v>
       </c>
       <c r="R34" t="n">
-        <v>6660307</v>
+        <v>6660356</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4337,12 +3986,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4358,12 +4007,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4374,53 +4023,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124450248</v>
+        <v>128760336</v>
       </c>
       <c r="B35" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>3739</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699796</v>
+        <v>699835</v>
       </c>
       <c r="R35" t="n">
-        <v>6660315</v>
+        <v>6660288</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4444,12 +4088,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,74 +4108,63 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124451555</v>
+        <v>82416827</v>
       </c>
       <c r="B36" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2008</v>
+        <v>3762</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699672</v>
+        <v>699838</v>
       </c>
       <c r="R36" t="n">
-        <v>6660331</v>
+        <v>6660371</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4555,12 +4188,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4569,33 +4202,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124454215</v>
+        <v>112662498</v>
       </c>
       <c r="B37" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4603,37 +4236,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221945</v>
+        <v>3762</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699929</v>
+        <v>699752</v>
       </c>
       <c r="R37" t="n">
-        <v>6660329</v>
+        <v>6660342</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4657,12 +4293,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4671,33 +4307,33 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124474452</v>
+        <v>128760311</v>
       </c>
       <c r="B38" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4705,21 +4341,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4729,10 +4365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699807</v>
+        <v>699951</v>
       </c>
       <c r="R38" t="n">
-        <v>6660377</v>
+        <v>6660298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4759,12 +4395,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4779,27 +4415,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124451595</v>
+        <v>130379973</v>
       </c>
       <c r="B39" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4807,34 +4438,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>3762</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699683</v>
+        <v>699820</v>
       </c>
       <c r="R39" t="n">
-        <v>6660350</v>
+        <v>6660145</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4861,12 +4492,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4877,31 +4508,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124446528</v>
+        <v>124474451</v>
       </c>
       <c r="B40" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4909,37 +4540,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>4189</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>699808</v>
+        <v>699943</v>
       </c>
       <c r="R40" t="n">
-        <v>6660347</v>
+        <v>6660307</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4977,33 +4611,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124451081</v>
+        <v>82416822</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5011,42 +4645,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699683</v>
+        <v>699838</v>
       </c>
       <c r="R41" t="n">
-        <v>6660350</v>
+        <v>6660371</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5070,12 +4702,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2019-10-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5084,71 +4716,74 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124445128</v>
+        <v>112662501</v>
       </c>
       <c r="B42" t="n">
-        <v>92326</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>699954</v>
+        <v>699752</v>
       </c>
       <c r="R42" t="n">
-        <v>6660370</v>
+        <v>6660342</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5172,12 +4807,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,76 +4821,74 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124445043</v>
+        <v>112662567</v>
       </c>
       <c r="B43" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>699954</v>
+        <v>699809</v>
       </c>
       <c r="R43" t="n">
-        <v>6660370</v>
+        <v>6660356</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5279,12 +4912,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5293,33 +4926,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124450058</v>
+        <v>128760327</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5327,37 +4960,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699808</v>
+        <v>699826</v>
       </c>
       <c r="R44" t="n">
-        <v>6660347</v>
+        <v>6660373</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5381,12 +5014,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5401,27 +5034,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124444956</v>
+        <v>112662570</v>
       </c>
       <c r="B45" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5429,37 +5057,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>4363</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699944</v>
+        <v>699809</v>
       </c>
       <c r="R45" t="n">
-        <v>6660374</v>
+        <v>6660356</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5483,12 +5114,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5497,33 +5128,33 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124449907</v>
+        <v>112662568</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5531,42 +5162,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>699754</v>
+        <v>699809</v>
       </c>
       <c r="R46" t="n">
-        <v>6660376</v>
+        <v>6660356</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5590,12 +5219,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5604,33 +5233,33 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124446732</v>
+        <v>128760313</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5638,34 +5267,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>699804</v>
+        <v>699942</v>
       </c>
       <c r="R47" t="n">
-        <v>6660392</v>
+        <v>6660292</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5692,12 +5321,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5712,66 +5341,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124447516</v>
+        <v>130379975</v>
       </c>
       <c r="B48" t="n">
-        <v>98324</v>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Svedjan, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699800</v>
+        <v>699783</v>
       </c>
       <c r="R48" t="n">
-        <v>6660415</v>
+        <v>6660083</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5798,12 +5418,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5814,64 +5434,72 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktor Lund, Martin Axegård</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128760320</v>
+        <v>112662497</v>
       </c>
       <c r="B49" t="n">
-        <v>91074</v>
+        <v>91424</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5747</v>
+        <v>5733</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Såpfingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria lutea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Vent.) Schild</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>699820</v>
+        <v>699752</v>
       </c>
       <c r="R49" t="n">
-        <v>6660298</v>
+        <v>6660342</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5895,64 +5523,69 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128760312</v>
+        <v>128760322</v>
       </c>
       <c r="B50" t="n">
-        <v>92871</v>
+        <v>91398</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>5745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5962,10 +5595,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699945</v>
+        <v>699806</v>
       </c>
       <c r="R50" t="n">
-        <v>6660298</v>
+        <v>6660365</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6024,48 +5657,51 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128760336</v>
+        <v>112662544</v>
       </c>
       <c r="B51" t="n">
-        <v>87023</v>
+        <v>91435</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3739</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699835</v>
+        <v>699830</v>
       </c>
       <c r="R51" t="n">
-        <v>6660288</v>
+        <v>6660298</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6089,12 +5725,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2023-10-11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6103,28 +5739,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128760333</v>
+        <v>128760320</v>
       </c>
       <c r="B52" t="n">
-        <v>87016</v>
+        <v>91435</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6132,38 +5773,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>449</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699668</v>
+        <v>699820</v>
       </c>
       <c r="R52" t="n">
-        <v>6660391</v>
+        <v>6660298</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6222,10 +5859,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128760316</v>
+        <v>128760334</v>
       </c>
       <c r="B53" t="n">
-        <v>91314</v>
+        <v>92928</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6233,21 +5870,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3215</v>
+        <v>5836</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6257,10 +5894,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699935</v>
+        <v>699664</v>
       </c>
       <c r="R53" t="n">
-        <v>6660294</v>
+        <v>6660365</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6319,48 +5956,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128760321</v>
+        <v>124444432</v>
       </c>
       <c r="B54" t="n">
-        <v>92824</v>
+        <v>93233</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699817</v>
+        <v>699938</v>
       </c>
       <c r="R54" t="n">
-        <v>6660321</v>
+        <v>6660298</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6384,12 +6021,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6404,22 +6041,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128760327</v>
+        <v>124445128</v>
       </c>
       <c r="B55" t="n">
-        <v>92827</v>
+        <v>93233</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6427,34 +6064,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>699826</v>
+        <v>699954</v>
       </c>
       <c r="R55" t="n">
-        <v>6660373</v>
+        <v>6660370</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6481,12 +6118,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6501,44 +6138,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128760313</v>
+        <v>128760312</v>
       </c>
       <c r="B56" t="n">
-        <v>92847</v>
+        <v>93233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6548,10 +6185,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699942</v>
+        <v>699945</v>
       </c>
       <c r="R56" t="n">
-        <v>6660292</v>
+        <v>6660298</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6610,48 +6247,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128760328</v>
+        <v>124449907</v>
       </c>
       <c r="B57" t="n">
-        <v>92824</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>150</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699826</v>
+        <v>699754</v>
       </c>
       <c r="R57" t="n">
-        <v>6660389</v>
+        <v>6660376</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6675,12 +6317,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6695,53 +6337,62 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128760323</v>
+        <v>124451081</v>
       </c>
       <c r="B58" t="n">
-        <v>87051</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>433</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Duvspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cortinarius caesiocanescens s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699814</v>
+        <v>699683</v>
       </c>
       <c r="R58" t="n">
-        <v>6660362</v>
+        <v>6660350</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6768,12 +6419,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6788,60 +6439,69 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128760322</v>
+        <v>130379971</v>
       </c>
       <c r="B59" t="n">
-        <v>91037</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5745</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, SSV om Hallstavik, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699806</v>
+        <v>699710</v>
       </c>
       <c r="R59" t="n">
-        <v>6660365</v>
+        <v>6660225</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6865,12 +6525,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6881,65 +6541,71 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128760317</v>
+        <v>124445043</v>
       </c>
       <c r="B60" t="n">
-        <v>92843</v>
+        <v>5179</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2058</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>699904</v>
+        <v>699954</v>
       </c>
       <c r="R60" t="n">
-        <v>6660284</v>
+        <v>6660370</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6966,12 +6632,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6986,57 +6652,62 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128760329</v>
+        <v>124447074</v>
       </c>
       <c r="B61" t="n">
-        <v>92843</v>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2058</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>699825</v>
+        <v>699804</v>
       </c>
       <c r="R61" t="n">
-        <v>6660385</v>
+        <v>6660392</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7063,12 +6734,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7083,22 +6754,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128760311</v>
+        <v>124444974</v>
       </c>
       <c r="B62" t="n">
-        <v>86795</v>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7106,34 +6777,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3762</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>699951</v>
+        <v>699954</v>
       </c>
       <c r="R62" t="n">
-        <v>6660298</v>
+        <v>6660370</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7160,12 +6836,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7180,61 +6856,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128760331</v>
+        <v>105298082</v>
       </c>
       <c r="B63" t="n">
-        <v>92845</v>
+        <v>99096</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>789</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>699784</v>
+        <v>699586</v>
       </c>
       <c r="R63" t="n">
-        <v>6660411</v>
+        <v>6660420</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7261,12 +6933,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7281,44 +6953,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128760337</v>
+        <v>105298083</v>
       </c>
       <c r="B64" t="n">
-        <v>92843</v>
+        <v>99096</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2058</v>
+        <v>219798</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7328,10 +7000,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>699843</v>
+        <v>699594</v>
       </c>
       <c r="R64" t="n">
-        <v>6660300</v>
+        <v>6660387</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7358,12 +7030,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7378,44 +7050,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128760324</v>
+        <v>105298085</v>
       </c>
       <c r="B65" t="n">
-        <v>92824</v>
+        <v>99096</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>150</v>
+        <v>219798</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7425,10 +7097,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>699814</v>
+        <v>699604</v>
       </c>
       <c r="R65" t="n">
-        <v>6660360</v>
+        <v>6660405</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7455,12 +7127,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7475,22 +7147,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128760326</v>
+        <v>124447516</v>
       </c>
       <c r="B66" t="n">
-        <v>92824</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7498,34 +7170,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>150</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>699824</v>
+        <v>699800</v>
       </c>
       <c r="R66" t="n">
-        <v>6660374</v>
+        <v>6660415</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7552,12 +7233,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7572,22 +7253,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128760334</v>
+        <v>124454215</v>
       </c>
       <c r="B67" t="n">
-        <v>92539</v>
+        <v>97983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7595,37 +7276,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5836</v>
+        <v>221945</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>699664</v>
+        <v>699929</v>
       </c>
       <c r="R67" t="n">
-        <v>6660365</v>
+        <v>6660329</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7649,12 +7330,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7669,44 +7350,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128760310</v>
+        <v>105298080</v>
       </c>
       <c r="B68" t="n">
-        <v>91000</v>
+        <v>101326</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3286</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7716,10 +7397,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>699951</v>
+        <v>699598</v>
       </c>
       <c r="R68" t="n">
-        <v>6660295</v>
+        <v>6660467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7746,12 +7427,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2022-10-10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7766,60 +7447,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Niina Sallmén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128760330</v>
+        <v>124444956</v>
       </c>
       <c r="B69" t="n">
-        <v>92843</v>
+        <v>101326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2058</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>699803</v>
+        <v>699944</v>
       </c>
       <c r="R69" t="n">
-        <v>6660408</v>
+        <v>6660374</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7843,12 +7524,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7863,60 +7544,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128760332</v>
+        <v>124446528</v>
       </c>
       <c r="B70" t="n">
-        <v>92299</v>
+        <v>101326</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>232138</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gul lammticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Albatrellus citrinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Ryman</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>699706</v>
+        <v>699808</v>
       </c>
       <c r="R70" t="n">
-        <v>6660389</v>
+        <v>6660347</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7940,12 +7621,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7960,64 +7641,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128760318</v>
+        <v>124450248</v>
       </c>
       <c r="B71" t="n">
-        <v>92843</v>
+        <v>101326</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2058</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>699868</v>
+        <v>699796</v>
       </c>
       <c r="R71" t="n">
-        <v>6660289</v>
+        <v>6660315</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8041,12 +7718,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8061,57 +7738,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128760325</v>
+        <v>124451595</v>
       </c>
       <c r="B72" t="n">
-        <v>92837</v>
+        <v>101326</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>788</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Lundås, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>699827</v>
+        <v>699683</v>
       </c>
       <c r="R72" t="n">
-        <v>6660373</v>
+        <v>6660350</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8138,12 +7815,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8158,69 +7835,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130379971</v>
+        <v>124452710</v>
       </c>
       <c r="B73" t="n">
-        <v>57861</v>
+        <v>101326</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Svedjan, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>699710</v>
+        <v>699855</v>
       </c>
       <c r="R73" t="n">
-        <v>6660225</v>
+        <v>6660145</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8244,12 +7912,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8260,31 +7928,26 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén</t>
+          <t>Viktor Lund, Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130379975</v>
+        <v>124474452</v>
       </c>
       <c r="B74" t="n">
-        <v>93083</v>
+        <v>101326</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8292,34 +7955,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>699783</v>
+        <v>699807</v>
       </c>
       <c r="R74" t="n">
-        <v>6660083</v>
+        <v>6660377</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8346,12 +8009,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8362,31 +8025,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130379973</v>
+        <v>124474453</v>
       </c>
       <c r="B75" t="n">
-        <v>87023</v>
+        <v>101326</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8394,34 +8052,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svedjan, SSV om Hallstavik, Upl</t>
+          <t>Lundås, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>699820</v>
+        <v>699934</v>
       </c>
       <c r="R75" t="n">
-        <v>6660145</v>
+        <v>6660275</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8448,12 +8106,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8464,24 +8122,731 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Äldre, grandominerad barrskog.</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>105298081</v>
+      </c>
+      <c r="B76" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>699637</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6660447</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>105298084</v>
+      </c>
+      <c r="B77" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>699592</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6660391</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>flera unga träd</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>105298088</v>
+      </c>
+      <c r="B78" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>699655</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6660307</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>105298089</v>
+      </c>
+      <c r="B79" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>699671</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6660294</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>ett par stycken ganska unga träd</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>105298090</v>
+      </c>
+      <c r="B80" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>699721</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6660259</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2022-10-10</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>ungt träd</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>112662524</v>
+      </c>
+      <c r="B81" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>699802</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6660244</v>
+      </c>
+      <c r="S81" t="n">
+        <v>25</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Eva Grönlund</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128760332</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92688</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lundås, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>699706</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6660389</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17406-2025 artfynd.xlsx
+++ b/artfynd/A 17406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416823</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760321</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760324</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760326</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124445502</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760323</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760333</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416824</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760331</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124446732</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447694</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450058</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2281,6 +2361,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416818</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2387,6 +2472,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451555</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2492,6 +2582,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416821</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662494</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,6 +2810,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662596</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2811,6 +2916,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760317</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760318</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3009,6 +3124,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760329</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3106,6 +3226,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760330</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3203,6 +3328,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760337</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3305,6 +3435,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124444867</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3402,6 +3537,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760316</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3499,6 +3639,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760310</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3600,6 +3745,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662551</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3705,6 +3855,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416825</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3810,6 +3965,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662525</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3915,6 +4075,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662546</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4020,6 +4185,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662602</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4117,6 +4287,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760336</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4222,6 +4397,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416827</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4327,6 +4507,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662498</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4424,6 +4609,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760311</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4526,6 +4716,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130379973</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4631,6 +4826,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124474451</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4736,6 +4936,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82416822</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4841,6 +5046,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662501</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4946,6 +5156,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662567</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5043,6 +5258,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760327</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5148,6 +5368,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662570</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5253,6 +5478,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662568</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5350,6 +5580,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760313</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5452,6 +5687,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130379975</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5557,6 +5797,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662497</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5654,6 +5899,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760322</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5759,6 +6009,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662544</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5856,6 +6111,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760320</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5953,6 +6213,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760334</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6050,6 +6315,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124444432</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6147,6 +6417,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124445128</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6244,6 +6519,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760312</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6346,6 +6626,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124449907</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6448,6 +6733,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451081</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6559,6 +6849,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130379971</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6661,6 +6956,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124445043</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6763,6 +7063,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447074</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6865,6 +7170,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124444974</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6962,6 +7272,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298082</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7059,6 +7374,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298083</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7156,6 +7476,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298085</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7262,6 +7587,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124447516</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7359,6 +7689,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124454215</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7456,6 +7791,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298080</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7553,6 +7893,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124444956</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7650,6 +7995,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124446528</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7747,6 +8097,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124450248</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7844,6 +8199,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124451595</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7941,6 +8301,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124452710</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8038,6 +8403,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124474452</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8135,6 +8505,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124474453</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8237,6 +8612,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298081</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8339,6 +8719,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298084</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8441,6 +8826,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298088</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8543,6 +8933,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298089</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8645,6 +9040,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105298090</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8750,6 +9150,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112662524</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8847,8 +9252,96 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760332</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>